--- a/DesignData/Excel_Masters/FamiliarAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/FamiliarAssets_Master.xlsx
@@ -1212,225 +1212,360 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>50</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/FamiliarAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/FamiliarAssets_Master.xlsx
@@ -9,226 +9,511 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21555" windowHeight="8040"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15420" windowHeight="10965"/>
   </bookViews>
   <sheets>
-    <sheet name="FamiliarStats_Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Tags" sheetId="2" r:id="rId2"/>
+    <sheet name="FamiliarAssets" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
-  <si>
-    <t>Unit.Attack.Melee</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Tanker</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Attack.Range</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Dealer</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Support</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="165">
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>FaceIcon</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>AIController</t>
+  </si>
+  <si>
+    <t>BehaviorTree</t>
+  </si>
+  <si>
+    <t>Blackboard</t>
+  </si>
+  <si>
+    <t>BasicAttackEffect</t>
+  </si>
+  <si>
+    <t>BasicAbility</t>
+  </si>
+  <si>
+    <t>SkillAbilities</t>
+  </si>
+  <si>
+    <t>ProjectileClass</t>
+  </si>
+  <si>
+    <t>BasicAttackEffectTag</t>
+  </si>
+  <si>
+    <t>SkeletalMesh</t>
+  </si>
+  <si>
+    <t>AnimBlueprint</t>
+  </si>
+  <si>
+    <t>AttackMontage</t>
+  </si>
+  <si>
+    <t>HitMontage</t>
+  </si>
+  <si>
+    <t>DeathMontage</t>
+  </si>
+  <si>
+    <t>UnitFXData</t>
+  </si>
+  <si>
+    <t>HitReactionTag</t>
   </si>
   <si>
     <t>BardFollower</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_BardFollower.Icon_BardFollower</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>(TagName="")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/BardFollower/SKM_BardFollower.SKM_BardFollower</t>
+  </si>
+  <si>
     <t>CherryBee</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_CherryBee.Icon_CherryBee</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/CherryBee/SKM_CherryBee.SKM_CherryBee</t>
+  </si>
+  <si>
     <t>CupFelice</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_CupFelice.Icon_CupFelice</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/CupFelice/SKM_CupFelice.SKM_CupFelice</t>
+  </si>
+  <si>
     <t>Dandelion</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Dandelion.Icon_Dandelion</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Dandelion/SKM_Dandelion.SKM_Dandelion</t>
+  </si>
+  <si>
     <t>DarumaNeko</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DarumaNeko.Icon_DarumaNeko</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/DarumaNeko/SKM_DarumaNeko.SKM_DarumaNeko</t>
+  </si>
+  <si>
     <t>Felice</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Felice.Icon_Felice</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Felice/SKM_Felice.SKM_Felice</t>
+  </si>
+  <si>
     <t>Firefly</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Firefly.Icon_Firefly</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Firefly/SKM_Firefly.SKM_Firefly</t>
+  </si>
+  <si>
     <t>ForestMacaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_ForestMacaron.Icon_ForestMacaron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/ForestMacaron/SKM_ForestMacaron.SKM_ForestMacaron</t>
+  </si>
+  <si>
     <t>ForestSpirit</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_ForestSpirit.Icon_ForestSpirit</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/ForestSpirit/SKM_ForestSpirit.SKM_ForestSpirit</t>
+  </si>
+  <si>
     <t>Foxhound</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FoxHound.Icon_FoxHound</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/KMJ/AI/BP_MyAIController_Range.BP_MyAIController_Range_C'</t>
+  </si>
+  <si>
+    <t>/Game/Test/KMJ/AI/BT_Monster_Ranged.BT_Monster_Ranged</t>
+  </si>
+  <si>
+    <t>/Game/Test/KMJ/AI/BB_Monster_Ranged.BB_Monster_Ranged</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_RangeBasicAttack.GA_RangeBasicAttack_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/YSM/BP_FireBall.BP_FireBall_C'</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Foxhound/SKM_Foxhound.SKM_Foxhound</t>
+  </si>
+  <si>
     <t>GoldMacaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GoldMacaron.Icon_GoldMacaron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/GoldMacaron/SKM_Gold_Macaron.SKM_Gold_Macaron</t>
+  </si>
+  <si>
     <t>Macaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Macaron.Icon_Macaron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Macaron/SKM_Macaron.SKM_Macaron</t>
+  </si>
+  <si>
     <t>MageMacaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MageMacaron.Icon_MageMacaron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/MageMacaron/SKM_MageMacaron.SKM_MageMacaron</t>
+  </si>
+  <si>
     <t>MagicPot</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MagicPot.Icon_MagicPot</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/MagicPot/SKM_MagicPot.SKM_MagicPot</t>
+  </si>
+  <si>
     <t>MinimiNeko</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MinimiNeko.Icon_MinimiNeko</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/MinimiNeko/SKM_MinimiNeko.SKM_MinimiNeko</t>
+  </si>
+  <si>
     <t>Mushroom</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mushroom.Icon_Mushroom</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Mushroom/SKM_Mushroom_A.SKM_Mushroom_A</t>
+  </si>
+  <si>
     <t>Oowl</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Oowl.Icon_Oowl</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Oowl/SKM_Oowl_A.SKM_Oowl_A</t>
+  </si>
+  <si>
     <t>ShieldMacaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_ShieldMacaron.Icon_ShieldMacaron</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/KMJ/AI/BP_MyAIController.BP_MyAIController_C'</t>
+  </si>
+  <si>
+    <t>/Game/Test/KMJ/AI/BT_Monster.BT_Monster</t>
+  </si>
+  <si>
+    <t>/Game/Test/KMJ/AI/BB_Monster.BB_Monster</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_MeleeBasicAttack.GA_MeleeBasicAttack_C'</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/ShieldMacaron/SKM_ShieldMacaron.SKM_ShieldMacaron</t>
+  </si>
+  <si>
     <t>Trumduck</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Trumduck.Icon_Trumduck</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Trumduck/SKM_Trumduck.SKM_Trumduck</t>
+  </si>
+  <si>
     <t>TunerFollower</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_TunerFollower.Icon_TunerFollower</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/TunerFollower/SKM_TunerFollower.SKM_TunerFollower</t>
+  </si>
+  <si>
     <t>Usami</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Usami.Icon_Usami</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Usami/SKM_Usami.SKM_Usami</t>
+  </si>
+  <si>
     <t>Messenger</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Messenger.Icon_Messenger</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Messenger/SKM_Messenger.SKM_Messenger</t>
+  </si>
+  <si>
     <t>Cannon</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Cannon.Icon_Cannon</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Cannon/SKM_Cannon.SKM_Cannon</t>
+  </si>
+  <si>
     <t>Fly</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Fly.Icon_Fly</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Fly/SKM_Fly.SKM_Fly</t>
+  </si>
+  <si>
     <t>Golem</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Golem.Icon_Golem</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Golem/SKM_Golem_A.SKM_Golem_A</t>
+  </si>
+  <si>
     <t>FelicisGuard</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FelicisGuard.Icon_FelicisGuard</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/FelicisGuard/SKM_FelicisGuard.SKM_FelicisGuard</t>
+  </si>
+  <si>
     <t>Clownfish</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Clownfish.Icon_Clownfish</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Clownfish/SKM_Clownfish.SKM_Clownfish</t>
+  </si>
+  <si>
     <t>FanOfDeath</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FanOfDeath.Icon_FanOfDeath</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/FanOfDeath/SKM_FanOfDeath.SKM_FanOfDeath</t>
+  </si>
+  <si>
     <t>CowardTurtle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_CowardTurtle.Icon_CowardTurtle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/CowardTurtle/SKM_CowardTurtle.SKM_CowardTurtle</t>
+  </si>
+  <si>
     <t>Imp</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Imp.Icon_Imp</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Imp/SKM_Imp.SKM_Imp</t>
+  </si>
+  <si>
     <t>Gemini_Book</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Gemini_Book.Icon_Gemini_Book</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Gemini_Book/SKM_Gemini_Book1.SKM_Gemini_Book1</t>
+  </si>
+  <si>
     <t>Turret</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Turret.Icon_Turret</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Turret/SKM_Turret.SKM_Turret</t>
+  </si>
+  <si>
     <t>Felicis</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Felicis.Icon_Felicis</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Felicis/SKM_Felicis.SKM_Felicis</t>
+  </si>
+  <si>
     <t>Tacodora</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Tacodora.Icon_Tacodora</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Tacodora/SKM_takodora_Weapon2.SKM_takodora_Weapon2</t>
+  </si>
+  <si>
     <t>KnightWolfron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_KnightWolfron.Icon_KnightWolfron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/KnightWolfron/SKM_KnightWolfron.SKM_KnightWolfron</t>
+  </si>
+  <si>
     <t>Leech</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Leech.Icon_Leech</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Leech/SKM_Leech.SKM_Leech</t>
+  </si>
+  <si>
     <t>NetherConnector</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_NetherConnector.Icon_NetherConnector</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/NetherConnector/SKM_NetherConnector.SKM_NetherConnector</t>
+  </si>
+  <si>
     <t>SmashingShrimp</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_SmashingShrimp.Icon_SmashingShrimp</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/SmashingShrimp/SKM_SmashingShrimp.SKM_SmashingShrimp</t>
+  </si>
+  <si>
     <t>ForestWolfron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_ForestWolfron.Icon_ForestWolfron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Wolfron/SKM_wolfron.SKM_wolfron</t>
+  </si>
+  <si>
     <t>Anemone</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Anemone.Icon_Anemone</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Anemone/SKM_Anemone.SKM_Anemone</t>
+  </si>
+  <si>
     <t>MummyMacaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MummyMacaron.Icon_MummyMacaron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/MummyMacaron/SKM_MummyMacaron_A.SKM_MummyMacaron_A</t>
+  </si>
+  <si>
     <t>Turtlog</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Turtlog.Icon_Turtlog</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Turtlog/SKM_Turtlog.SKM_Turtlog</t>
+  </si>
+  <si>
     <t>Bat</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Bat.Icon_Bat</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Bat/SKM_Bat.SKM_Bat</t>
+  </si>
+  <si>
     <t>Mask</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mask.Icon_Mask</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Mask/SKM_Mask.SKM_Mask</t>
+  </si>
+  <si>
     <t>GuardianTreantMini</t>
   </si>
   <si>
-    <t>SkeletalMesh</t>
-  </si>
-  <si>
-    <t>AnimBlueprint</t>
-  </si>
-  <si>
-    <t>AttackMontage</t>
-  </si>
-  <si>
-    <t>HitMontage</t>
-  </si>
-  <si>
-    <t>DeathMontage</t>
-  </si>
-  <si>
-    <t>VoiceDataAsset</t>
-  </si>
-  <si>
-    <t>HitReactionTag</t>
-  </si>
-  <si>
-    <t>FaceIcon</t>
-  </si>
-  <si>
-    <t>Scale</t>
-  </si>
-  <si>
-    <t>AIController</t>
-  </si>
-  <si>
-    <t>BehaviorTree</t>
-  </si>
-  <si>
-    <t>Blackboard</t>
-  </si>
-  <si>
-    <t>BasicAttackEffect</t>
-  </si>
-  <si>
-    <t>BasicAbility</t>
-  </si>
-  <si>
-    <t>SkillAbilities</t>
-  </si>
-  <si>
-    <t>ProjectileClass</t>
-  </si>
-  <si>
-    <t>BasicAttackEffectTag</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GuardianTreantMini.Icon_GuardianTreantMini</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/GuardianTreantMini/SKM_GuardianTreantMini.SKM_GuardianTreantMini</t>
   </si>
 </sst>
 </file>
@@ -1148,501 +1433,2446 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="6" max="6" width="9.125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" t="s">
-        <v>55</v>
-      </c>
       <c r="G1" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" t="s">
+        <v>20</v>
+      </c>
+      <c r="P4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" t="s">
+        <v>20</v>
+      </c>
+      <c r="P6" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O7" t="s">
+        <v>20</v>
+      </c>
+      <c r="P7" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>20</v>
+      </c>
+      <c r="R7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" t="s">
+        <v>20</v>
+      </c>
+      <c r="N8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" t="s">
+        <v>20</v>
+      </c>
+      <c r="P8" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R8" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" t="s">
+        <v>20</v>
+      </c>
+      <c r="O9" t="s">
+        <v>20</v>
+      </c>
+      <c r="P9" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>20</v>
+      </c>
+      <c r="R9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" t="s">
+        <v>20</v>
+      </c>
+      <c r="O10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>20</v>
+      </c>
+      <c r="R10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" t="s">
+        <v>54</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" t="s">
+        <v>20</v>
+      </c>
+      <c r="P11" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>20</v>
+      </c>
+      <c r="R11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12" t="s">
+        <v>20</v>
+      </c>
+      <c r="P12" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>20</v>
+      </c>
+      <c r="R12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
+        <v>59</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N13" t="s">
+        <v>20</v>
+      </c>
+      <c r="O13" t="s">
+        <v>20</v>
+      </c>
+      <c r="P13" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>20</v>
+      </c>
+      <c r="R13" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M14" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" t="s">
+        <v>20</v>
+      </c>
+      <c r="O14" t="s">
+        <v>20</v>
+      </c>
+      <c r="P14" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>20</v>
+      </c>
+      <c r="R14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M15" t="s">
+        <v>20</v>
+      </c>
+      <c r="N15" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15" t="s">
+        <v>20</v>
+      </c>
+      <c r="P15" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>20</v>
+      </c>
+      <c r="R15" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" t="s">
+        <v>20</v>
+      </c>
+      <c r="P16" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>20</v>
+      </c>
+      <c r="R16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>82</v>
+      </c>
+      <c r="J17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" t="s">
+        <v>73</v>
+      </c>
+      <c r="M17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>20</v>
+      </c>
+      <c r="R17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>82</v>
+      </c>
+      <c r="J18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" t="s">
+        <v>76</v>
+      </c>
+      <c r="M18" t="s">
+        <v>20</v>
+      </c>
+      <c r="N18" t="s">
+        <v>20</v>
+      </c>
+      <c r="O18" t="s">
+        <v>20</v>
+      </c>
+      <c r="P18" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>20</v>
+      </c>
+      <c r="R18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" t="s">
+        <v>82</v>
+      </c>
+      <c r="J19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" t="s">
+        <v>83</v>
+      </c>
+      <c r="M19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" t="s">
+        <v>20</v>
+      </c>
+      <c r="P19" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>20</v>
+      </c>
+      <c r="R19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" t="s">
+        <v>86</v>
+      </c>
+      <c r="M20" t="s">
+        <v>20</v>
+      </c>
+      <c r="N20" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" t="s">
+        <v>20</v>
+      </c>
+      <c r="P20" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" t="s">
+        <v>54</v>
+      </c>
+      <c r="K21" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" t="s">
+        <v>89</v>
+      </c>
+      <c r="M21" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" t="s">
+        <v>20</v>
+      </c>
+      <c r="P21" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>20</v>
+      </c>
+      <c r="R21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" t="s">
+        <v>92</v>
+      </c>
+      <c r="M22" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22" t="s">
+        <v>20</v>
+      </c>
+      <c r="P22" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>20</v>
+      </c>
+      <c r="R22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="B23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" t="s">
+        <v>82</v>
+      </c>
+      <c r="J23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" t="s">
+        <v>95</v>
+      </c>
+      <c r="M23" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" t="s">
+        <v>20</v>
+      </c>
+      <c r="O23" t="s">
+        <v>20</v>
+      </c>
+      <c r="P23" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>20</v>
+      </c>
+      <c r="R23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>28</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" t="s">
+        <v>98</v>
+      </c>
+      <c r="M24" t="s">
+        <v>20</v>
+      </c>
+      <c r="N24" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" t="s">
+        <v>20</v>
+      </c>
+      <c r="P24" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>20</v>
+      </c>
+      <c r="R24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" t="s">
+        <v>54</v>
+      </c>
+      <c r="K25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" t="s">
+        <v>101</v>
+      </c>
+      <c r="M25" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" t="s">
+        <v>20</v>
+      </c>
+      <c r="P25" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>20</v>
+      </c>
+      <c r="R25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" t="s">
+        <v>53</v>
+      </c>
+      <c r="J26" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" t="s">
+        <v>104</v>
+      </c>
+      <c r="M26" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" t="s">
+        <v>20</v>
+      </c>
+      <c r="O26" t="s">
+        <v>20</v>
+      </c>
+      <c r="P26" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>20</v>
+      </c>
+      <c r="R26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="B27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" t="s">
+        <v>82</v>
+      </c>
+      <c r="J27" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" t="s">
+        <v>107</v>
+      </c>
+      <c r="M27" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" t="s">
+        <v>20</v>
+      </c>
+      <c r="P27" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>20</v>
+      </c>
+      <c r="R27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J28" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" t="s">
+        <v>110</v>
+      </c>
+      <c r="M28" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" t="s">
+        <v>20</v>
+      </c>
+      <c r="P28" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>20</v>
+      </c>
+      <c r="R28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J29" t="s">
+        <v>54</v>
+      </c>
+      <c r="K29" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" t="s">
+        <v>113</v>
+      </c>
+      <c r="M29" t="s">
+        <v>20</v>
+      </c>
+      <c r="N29" t="s">
+        <v>20</v>
+      </c>
+      <c r="O29" t="s">
+        <v>20</v>
+      </c>
+      <c r="P29" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>20</v>
+      </c>
+      <c r="R29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="B30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" t="s">
+        <v>116</v>
+      </c>
+      <c r="M30" t="s">
+        <v>20</v>
+      </c>
+      <c r="N30" t="s">
+        <v>20</v>
+      </c>
+      <c r="O30" t="s">
+        <v>20</v>
+      </c>
+      <c r="P30" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>20</v>
+      </c>
+      <c r="R30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="B31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" t="s">
+        <v>82</v>
+      </c>
+      <c r="J31" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" t="s">
+        <v>119</v>
+      </c>
+      <c r="M31" t="s">
+        <v>20</v>
+      </c>
+      <c r="N31" t="s">
+        <v>20</v>
+      </c>
+      <c r="O31" t="s">
+        <v>20</v>
+      </c>
+      <c r="P31" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>20</v>
+      </c>
+      <c r="R31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>36</v>
-      </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="B32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" t="s">
+        <v>82</v>
+      </c>
+      <c r="J32" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" t="s">
+        <v>122</v>
+      </c>
+      <c r="M32" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32" t="s">
+        <v>20</v>
+      </c>
+      <c r="P32" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>20</v>
+      </c>
+      <c r="R32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="B33" t="s">
+        <v>124</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" t="s">
+        <v>81</v>
+      </c>
+      <c r="G33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" t="s">
+        <v>82</v>
+      </c>
+      <c r="J33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" t="s">
+        <v>125</v>
+      </c>
+      <c r="M33" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33" t="s">
+        <v>20</v>
+      </c>
+      <c r="P33" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>20</v>
+      </c>
+      <c r="R33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+      <c r="B34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J34" t="s">
+        <v>54</v>
+      </c>
+      <c r="K34" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" t="s">
+        <v>128</v>
+      </c>
+      <c r="M34" t="s">
+        <v>20</v>
+      </c>
+      <c r="N34" t="s">
+        <v>20</v>
+      </c>
+      <c r="O34" t="s">
+        <v>20</v>
+      </c>
+      <c r="P34" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>20</v>
+      </c>
+      <c r="R34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="B35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>79</v>
+      </c>
+      <c r="E35" t="s">
+        <v>80</v>
+      </c>
+      <c r="F35" t="s">
+        <v>81</v>
+      </c>
+      <c r="G35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" t="s">
+        <v>82</v>
+      </c>
+      <c r="J35" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" t="s">
+        <v>131</v>
+      </c>
+      <c r="M35" t="s">
+        <v>20</v>
+      </c>
+      <c r="N35" t="s">
+        <v>20</v>
+      </c>
+      <c r="O35" t="s">
+        <v>20</v>
+      </c>
+      <c r="P35" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>20</v>
+      </c>
+      <c r="R35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>40</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+      <c r="B36" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H36" t="s">
+        <v>82</v>
+      </c>
+      <c r="J36" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" t="s">
+        <v>134</v>
+      </c>
+      <c r="M36" t="s">
+        <v>20</v>
+      </c>
+      <c r="N36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O36" t="s">
+        <v>20</v>
+      </c>
+      <c r="P36" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>20</v>
+      </c>
+      <c r="R36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>41</v>
-      </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+      <c r="B37" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37" t="s">
+        <v>52</v>
+      </c>
+      <c r="H37" t="s">
+        <v>53</v>
+      </c>
+      <c r="J37" t="s">
+        <v>54</v>
+      </c>
+      <c r="K37" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" t="s">
+        <v>137</v>
+      </c>
+      <c r="M37" t="s">
+        <v>20</v>
+      </c>
+      <c r="N37" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37" t="s">
+        <v>20</v>
+      </c>
+      <c r="P37" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>20</v>
+      </c>
+      <c r="R37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>42</v>
-      </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="B38" t="s">
+        <v>139</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" t="s">
+        <v>81</v>
+      </c>
+      <c r="G38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H38" t="s">
+        <v>82</v>
+      </c>
+      <c r="J38" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" t="s">
+        <v>140</v>
+      </c>
+      <c r="M38" t="s">
+        <v>20</v>
+      </c>
+      <c r="N38" t="s">
+        <v>20</v>
+      </c>
+      <c r="O38" t="s">
+        <v>20</v>
+      </c>
+      <c r="P38" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>20</v>
+      </c>
+      <c r="R38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>43</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+      <c r="B39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39" t="s">
+        <v>81</v>
+      </c>
+      <c r="G39" t="s">
+        <v>52</v>
+      </c>
+      <c r="H39" t="s">
+        <v>82</v>
+      </c>
+      <c r="J39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" t="s">
+        <v>143</v>
+      </c>
+      <c r="M39" t="s">
+        <v>20</v>
+      </c>
+      <c r="N39" t="s">
+        <v>20</v>
+      </c>
+      <c r="O39" t="s">
+        <v>20</v>
+      </c>
+      <c r="P39" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>20</v>
+      </c>
+      <c r="R39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>44</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G40" t="s">
+        <v>52</v>
+      </c>
+      <c r="H40" t="s">
+        <v>82</v>
+      </c>
+      <c r="J40" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" t="s">
+        <v>146</v>
+      </c>
+      <c r="M40" t="s">
+        <v>20</v>
+      </c>
+      <c r="N40" t="s">
+        <v>20</v>
+      </c>
+      <c r="O40" t="s">
+        <v>20</v>
+      </c>
+      <c r="P40" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>20</v>
+      </c>
+      <c r="R40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>45</v>
-      </c>
-      <c r="J41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="B41" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" t="s">
+        <v>80</v>
+      </c>
+      <c r="F41" t="s">
+        <v>81</v>
+      </c>
+      <c r="G41" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" t="s">
+        <v>82</v>
+      </c>
+      <c r="J41" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" t="s">
+        <v>149</v>
+      </c>
+      <c r="M41" t="s">
+        <v>20</v>
+      </c>
+      <c r="N41" t="s">
+        <v>20</v>
+      </c>
+      <c r="O41" t="s">
+        <v>20</v>
+      </c>
+      <c r="P41" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>20</v>
+      </c>
+      <c r="R41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>46</v>
-      </c>
-      <c r="J42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="B42" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" t="s">
+        <v>80</v>
+      </c>
+      <c r="F42" t="s">
+        <v>81</v>
+      </c>
+      <c r="G42" t="s">
+        <v>52</v>
+      </c>
+      <c r="H42" t="s">
+        <v>82</v>
+      </c>
+      <c r="J42" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" t="s">
+        <v>152</v>
+      </c>
+      <c r="M42" t="s">
+        <v>20</v>
+      </c>
+      <c r="N42" t="s">
+        <v>20</v>
+      </c>
+      <c r="O42" t="s">
+        <v>20</v>
+      </c>
+      <c r="P42" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>20</v>
+      </c>
+      <c r="R42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>47</v>
-      </c>
-      <c r="J43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+      <c r="B43" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F43" t="s">
+        <v>81</v>
+      </c>
+      <c r="G43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J43" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" t="s">
+        <v>155</v>
+      </c>
+      <c r="M43" t="s">
+        <v>20</v>
+      </c>
+      <c r="N43" t="s">
+        <v>20</v>
+      </c>
+      <c r="O43" t="s">
+        <v>20</v>
+      </c>
+      <c r="P43" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>20</v>
+      </c>
+      <c r="R43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>48</v>
-      </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+      <c r="B44" t="s">
+        <v>157</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" t="s">
+        <v>80</v>
+      </c>
+      <c r="F44" t="s">
+        <v>81</v>
+      </c>
+      <c r="G44" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" t="s">
+        <v>82</v>
+      </c>
+      <c r="J44" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" t="s">
+        <v>158</v>
+      </c>
+      <c r="M44" t="s">
+        <v>20</v>
+      </c>
+      <c r="N44" t="s">
+        <v>20</v>
+      </c>
+      <c r="O44" t="s">
+        <v>20</v>
+      </c>
+      <c r="P44" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>20</v>
+      </c>
+      <c r="R44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
         <v>49</v>
       </c>
-      <c r="J45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" t="s">
+        <v>51</v>
+      </c>
+      <c r="G45" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45" t="s">
+        <v>53</v>
+      </c>
+      <c r="J45" t="s">
+        <v>54</v>
+      </c>
+      <c r="K45" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" t="s">
+        <v>161</v>
+      </c>
+      <c r="M45" t="s">
+        <v>20</v>
+      </c>
+      <c r="N45" t="s">
+        <v>20</v>
+      </c>
+      <c r="O45" t="s">
+        <v>20</v>
+      </c>
+      <c r="P45" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>20</v>
+      </c>
+      <c r="R45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>50</v>
-      </c>
-      <c r="J46">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <dataValidations count="8">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="중복된 ID (RowName Error)" error="이미 존재하는 ID입니다!_x000a__x000a_RowName(행 이름)은 고유해야 합니다._x000a_(같은 이름을 두 번 쓸 수 없습니다.)" sqref="A2:A1048576">
-      <formula1>COUNTIF($A:$A, A2) &lt;= 1</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="확률 범위 오류 (0~1)" error="확률은 0.0 ~ 1.0 사이의 값만 가능합니다._x000a__x000a_[올바른 예시]_x000a_- 10% -&gt; 0.1 입력_x000a_- 50% -&gt; 0.5 입력_x000a_- 100% -&gt; 1.0 입력" sqref="M1:M1048576">
-      <formula1>0</formula1>
-      <formula2>1</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="스탯 입력 오류" error="기본 스탯은 음수(-)일 수 없습니다._x000a_0 이상의 값을 입력해주세요." sqref="I1:K1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="최소 체력 오류" error="최대 체력(MaxHP)은 최소 1 이상이어야 합니다._x000a_0을 입력하면 유닛이 생성되자마자 죽습니다!" sqref="H1:H1048576">
-      <formula1>1</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류 (Speed)" error="속도는 0보다 작을 수 없습니다._x000a_언리얼 단위(cm/s)입니다._x000a_(예: 100 = 1미터, 600 = 달리기 속도)" sqref="L1:L1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류(Range)" error="공격 사거리는 0보다 작을 수 없습니다._x000a_(예: 100 = 1미터)" sqref="F1:F1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="단위 확인 (Cooldown)" error="쿨타임은 0보다 작을 수 없습니다._x000a__x000a_※ 단위: 초 (Seconds)_x000a_- 1분 = '60' 입력_x000a_- 0.5초 = '0.5' 입력_x000a_- 쿨타임 없음 = '0' 입력_x000a__x000a_밀리초(ms) 단위가 아닙니다! 다시 확인해주세요." sqref="G2:G1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)와 0은 입력할 수 없습니다. 0 보다 큰 숫자를 입력해주세요." sqref="E2:E1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Tags!$A$1:$A$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Tags!$B$1:$B$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>4</v>
+        <v>162</v>
+      </c>
+      <c r="B46" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" t="s">
+        <v>80</v>
+      </c>
+      <c r="F46" t="s">
+        <v>81</v>
+      </c>
+      <c r="G46" t="s">
+        <v>52</v>
+      </c>
+      <c r="H46" t="s">
+        <v>82</v>
+      </c>
+      <c r="J46" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" t="s">
+        <v>164</v>
+      </c>
+      <c r="M46" t="s">
+        <v>20</v>
+      </c>
+      <c r="N46" t="s">
+        <v>20</v>
+      </c>
+      <c r="O46" t="s">
+        <v>20</v>
+      </c>
+      <c r="P46" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>20</v>
+      </c>
+      <c r="R46" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/FamiliarAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/FamiliarAssets_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="340">
   <si>
     <t>---</t>
   </si>
@@ -168,24 +168,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FoxHound.Icon_FoxHound</t>
   </si>
   <si>
-    <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/KMJ/AI/BP_MyAIController_Range.BP_MyAIController_Range_C'</t>
-  </si>
-  <si>
-    <t>/Game/Test/KMJ/AI/BT_Monster_Ranged.BT_Monster_Ranged</t>
-  </si>
-  <si>
-    <t>/Game/Test/KMJ/AI/BB_Monster_Ranged.BB_Monster_Ranged</t>
-  </si>
-  <si>
     <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'</t>
   </si>
   <si>
-    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_RangeBasicAttack.GA_RangeBasicAttack_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/YSM/BP_FireBall.BP_FireBall_C'</t>
-  </si>
-  <si>
     <t>/Game/External_Assets/Monster/Foxhound/SKM_Foxhound.SKM_Foxhound</t>
   </si>
   <si>
@@ -514,6 +499,546 @@
   </si>
   <si>
     <t>/Game/External_Assets/Monster/GuardianTreantMini/SKM_GuardianTreantMini.SKM_GuardianTreantMini</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/BardFollower/AM_BardFollower_Attack.AM_BardFollower_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/BardFollower/AM_BardFollower_Damage.AM_BardFollower_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/BardFollower/AM_BardFollower_Dead.AM_BardFollower_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/BardFollower/ABP_BardFollower.ABP_BardFollower_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/CherryBee/ABP_CherryBee.ABP_CherryBee_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/CherryBee/AM_CherryBee_Attack.AM_CherryBee_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/CherryBee/AM_CherryBee_Damage.AM_CherryBee_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/CherryBee/AM_CherryBee_Dead.AM_CherryBee_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/CupFelice/ABP_CupFelice.ABP_CupFelice_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/CupFelice/AM_CupFelice_Attack.AM_CupFelice_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/CupFelice/AM_CupFelice_Damage.AM_CupFelice_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/CupFelice/AM_CupFelice_Dead.AM_CupFelice_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Dandelion/ABP_Dandelion.ABP_Dandelion_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Dandelion/AM_Dandelion_Attack.AM_Dandelion_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Dandelion/AM_Dandelion_Damage.AM_Dandelion_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Dandelion/AM_Dandelion_Dead.AM_Dandelion_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/DarumaNeko/ABP_DarumaNeko.ABP_DarumaNeko_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/DarumaNeko/AM_DarumaNeko_Attack.AM_DarumaNeko_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/DarumaNeko/AM_DarumaNeko_Damage.AM_DarumaNeko_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/DarumaNeko/AM_DarumaNeko_Dead.AM_DarumaNeko_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Felice/ABP_Felice.ABP_Felice_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Felice/AM_Felice_Attack.AM_Felice_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Felice/AM_Felice_Damage.AM_Felice_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Felice/AM_Felice_Dead.AM_Felice_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Firefly/ABP_Firefly.ABP_Firefly_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Firefly/AM_Firefly_Attack.AM_Firefly_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Firefly/AM_Firefly_Damage.AM_Firefly_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Firefly/AM_Firefly_Dead.AM_Firefly_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/ForestMacaron/ABP_ForestMacaron.ABP_ForestMacaron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ForestMacaron/AM_ForestMacaron_Attack.AM_ForestMacaron_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ForestMacaron/AM_ForestMacaron_Damage.AM_ForestMacaron_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ForestMacaron/AM_ForestMacaron_Dead.AM_ForestMacaron_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/ForestSpirit/ABP_ForestSpirit.ABP_ForestSpirit_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ForestSpirit/AM_ForestSpirit_Attack.AM_ForestSpirit_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ForestSpirit/AM_ForestSpirit_Damage.AM_ForestSpirit_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ForestSpirit/AM_ForestSpirit_Dead.AM_ForestSpirit_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Foxhound/ABP_Foxhound.ABP_Foxhound_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Attack.AM_Foxhound_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Damage.AM_Foxhound_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Dead.AM_Foxhound_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/GoldMacaron/ABP_GoldMacaron.ABP_GoldMacaron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/GoldMacaron/AM_GoldMacaron_Attack.AM_GoldMacaron_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/GoldMacaron/AM_GoldMacaron_Damage.AM_GoldMacaron_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/GoldMacaron/AM_GoldMacaron_Dead.AM_GoldMacaron_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Macaron/ABP_Macaron.ABP_Macaron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Macaron/AM_Macaron_Attack.AM_Macaron_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Macaron/AM_Macaron_Damage.AM_Macaron_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Macaron/AM_Macaron_Dead.AM_Macaron_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MageMacaron/ABP_MageMacaron.ABP_MageMacaron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MageMacaron/AM_MageMacaron_Attack.AM_MageMacaron_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MageMacaron/AM_MageMacaron_Damage.AM_MageMacaron_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MageMacaron/AM_MageMacaron_Dead.AM_MageMacaron_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MagicPot/ABP_MagicPot.ABP_MagicPot_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MagicPot/AM_MagicPot_Attack.AM_MagicPot_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MagicPot/AM_MagicPot_Damage.AM_MagicPot_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MagicPot/AM_MagicPot_Dead.AM_MagicPot_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MinimiNeko/ABP_MinimiNeko.ABP_MinimiNeko_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MinimiNeko/AM_MinimiNeko_Attack.AM_MinimiNeko_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MinimiNeko/AM_MinimiNeko_Damage.AM_MinimiNeko_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MinimiNeko/AM_MinimiNeko_Dead.AM_MinimiNeko_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Mushroom/ABP_Mushroom.ABP_Mushroom_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Mushroom/AM_Mushroom_Attack.AM_Mushroom_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Mushroom/AM_Mushroom_Damage.AM_Mushroom_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Mushroom/AM_Mushroom_Dead.AM_Mushroom_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Oowl/ABP_Oowl.ABP_Oowl_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Oowl/AM_Oowl_Attack.AM_Oowl_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Oowl/AM_Oowl_Damage.AM_Oowl_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Oowl/AM_Oowl_Dead.AM_Oowl_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/ShieldMacaron/ABP_ShieldMacaron.ABP_ShieldMacaron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ShieldMacaron/AM_ShieldMacaron_Attack.AM_ShieldMacaron_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ShieldMacaron/AM_ShieldMacaron_Damage.AM_ShieldMacaron_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ShieldMacaron/AM_ShieldMacaron_Dead.AM_ShieldMacaron_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Trumduck/ABP_Trumduck.ABP_Trumduck_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Trumduck/AM_Trumduck_Attack.AM_Trumduck_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Trumduck/AM_Trumduck_Damage.AM_Trumduck_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Trumduck/AM_Trumduck_Dead.AM_Trumduck_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/TunerFollower/ABP_TunerFollower.ABP_TunerFollower_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/TunerFollower/AM_TunerFollower_Attack.AM_TunerFollower_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/TunerFollower/AM_TunerFollower_Damage.AM_TunerFollower_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/TunerFollower/AM_TunerFollower_Dead.AM_TunerFollower_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Usami/ABP_Usami.ABP_Usami_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Usami/AM_Usami_Attack.AM_Usami_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Usami/AM_Usami_Damage.AM_Usami_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Usami/AM_Usami_Dead.AM_Usami_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Messenger/ABP_Messenger.ABP_Messenger_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Messenger/AM_Messenger_Attack.AM_Messenger_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Messenger/AM_Messenger_Damage.AM_Messenger_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Messenger/AM_Messenger_Dead.AM_Messenger_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Cannon/ABP_Cannon.ABP_Cannon_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Cannon/AM_Cannon_Attack.AM_Cannon_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Cannon/AM_Cannon_Damage.AM_Cannon_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Cannon/AM_Cannon_Dead.AM_Cannon_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Fly/ABP_Fly.ABP_Fly_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Fly/AM_Fly_Attack.AM_Fly_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Fly/AM_Fly_Damage.AM_Fly_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Fly/AM_Fly_Dead.AM_Fly_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Golem/ABP_Golem.ABP_Golem_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Golem/AM_Golem_Attack.AM_Golem_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Golem/AM_Golem_Damage.AM_Golem_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Golem/AM_Golem_Dead.AM_Golem_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/FelicisGuard/ABP_FelicisGuard.ABP_FelicisGuard_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/FelicisGuard/AM_FelicisGuard_Attack.AM_FelicisGuard_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/FelicisGuard/AM_FelicisGuard_Damage.AM_FelicisGuard_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/FelicisGuard/AM_FelicisGuard_Dead.AM_FelicisGuard_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Clownfish/ABP_Clownfish.ABP_Clownfish_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Clownfish/AM_Clownfish_Attack.AM_Clownfish_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Clownfish/AM_Clownfish_Damage.AM_Clownfish_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Clownfish/AM_Clownfish_Dead.AM_Clownfish_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/FanOfDeath/ABP_FanOfDeath.ABP_FanOfDeath_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/FanOfDeath/AM_FanOfDeath_Attack.AM_FanOfDeath_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/FanOfDeath/AM_FanOfDeath_Damage.AM_FanOfDeath_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/FanOfDeath/AM_FanOfDeath_Dead.AM_FanOfDeath_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/CowardTurtle/ABP_CowardTurtle.ABP_CowardTurtle_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/CowardTurtle/AM_CowardTurtle_Attack.AM_CowardTurtle_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/CowardTurtle/AM_CowardTurtle_Damage.AM_CowardTurtle_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/CowardTurtle/AM_CowardTurtle_Dead.AM_CowardTurtle_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Imp/ABP_Imp.ABP_Imp_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Imp/AM_Imp_Attack.AM_Imp_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Imp/AM_Imp_Damage.AM_Imp_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Imp/AM_Imp_Dead.AM_Imp_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Gemini_Book/ABP_Gemini_Book.ABP_Gemini_Book_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Gemini_Book/AM_Gemini_Book_Attack.AM_Gemini_Book_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Gemini_Book/AM_Gemini_Book_Damage.AM_Gemini_Book_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Gemini_Book/AM_Gemini_Book_Dead.AM_Gemini_Book_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Turret/ABP_Turret.ABP_Turret_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Turret/AM_Turret_Attack.AM_Turret_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Turret/AM_Turret_Damage.AM_Turret_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Turret/AM_Turret_Dead.AM_Turret_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Felicis/ABP_Felicis.ABP_Felicis_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Felicis/AM_Felicis_Attack.AM_Felicis_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Felicis/AM_Felicis_Damage.AM_Felicis_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Felicis/AM_Felicis_Dead.AM_Felicis_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Tacodora/ABP_Tacodora.ABP_Tacodora_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Tacodora/AM_Tacodora_Attack.AM_Tacodora_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Tacodora/AM_Tacodora_Damage.AM_Tacodora_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Tacodora/AM_Tacodora_Dead.AM_Tacodora_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/KnightWolfron/ABP_KnightWolfron.ABP_KnightWolfron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/KnightWolfron/AM_KnightWolfron_Attack.AM_KnightWolfron_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/KnightWolfron/AM_KnightWolfron_Damage.AM_KnightWolfron_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/KnightWolfron/AM_KnightWolfron_Dead.AM_KnightWolfron_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Leech/ABP_Leech.ABP_Leech_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Leech/AM_Leech_Attack.AM_Leech_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Leech/AM_Leech_Damage.AM_Leech_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Leech/AM_Leech_Dead.AM_Leech_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/NetherConnector/ABP_NetherConnector.ABP_NetherConnector_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/NetherConnector/AM_NetherConnector_Attack.AM_NetherConnector_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/NetherConnector/AM_NetherConnector_Damage.AM_NetherConnector_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/NetherConnector/AM_NetherConnector_Dead.AM_NetherConnector_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/SmashingShrimp/ABP_SmashingShrimp.ABP_SmashingShrimp_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/SmashingShrimp/AM_SmashingShrimp_Attack.AM_SmashingShrimp_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/SmashingShrimp/AM_SmashingShrimp_Damage.AM_SmashingShrimp_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/SmashingShrimp/AM_SmashingShrimp_Dead.AM_SmashingShrimp_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/ForestWolfron/ABP_ForestWolfron.ABP_ForestWolfron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ForestWolfron/AM_ForestWolfron_Attack.AM_ForestWolfron_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ForestWolfron/AM_ForestWolfron_Damage.AM_ForestWolfron_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/ForestWolfron/AM_ForestWolfron_Dead.AM_ForestWolfron_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Anemone/ABP_Anemone.ABP_Anemone_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Anemone/AM_Anemone_Attack.AM_Anemone_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Anemone/AM_Anemone_Damage.AM_Anemone_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Anemone/AM_Anemone_Dead.AM_Anemone_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MummyMacaron/ABP_MummyMacaron.ABP_MummyMacaron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MummyMacaron/AM_MummyMacaron_Attack.AM_MummyMacaron_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MummyMacaron/AM_MummyMacaron_Damage.AM_MummyMacaron_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/MummyMacaron/AM_MummyMacaron_Dead.AM_MummyMacaron_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Turtlog/ABP_Turtlog.ABP_Turtlog_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Turtlog/AM_Turtlog_Attack.AM_Turtlog_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Turtlog/AM_Turtlog_Damage.AM_Turtlog_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Turtlog/AM_Turtlog_Dead.AM_Turtlog_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Bat/ABP_Bat.ABP_Bat_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Bat/AM_Bat_Attack.AM_Bat_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Bat/AM_Bat_Damage.AM_Bat_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Bat/AM_Bat_Dead.AM_Bat_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Mask/ABP_Mask.ABP_Mask_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Mask/AM_Mask_Attack.AM_Mask_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Mask/AM_Mask_Damage.AM_Mask_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/Mask/AM_Mask_Dead.AM_Mask_Dead'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/GuardianTreantMini/ABP_GuardianTreantMini.ABP_GuardianTreantMini_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/GuardianTreantMini/AM_GuardianTreantMini_Attack.AM_GuardianTreantMini_Attack'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/GuardianTreantMini/AM_GuardianTreantMini_Damage.AM_GuardianTreantMini_Damage'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Blueprints/Characters/Familiar/GuardianTreantMini/AM_GuardianTreantMini_Dead.AM_GuardianTreantMini_Dead'</t>
   </si>
 </sst>
 </file>
@@ -1501,19 +2026,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
@@ -1525,16 +2050,16 @@
         <v>22</v>
       </c>
       <c r="M2" t="s">
-        <v>20</v>
+        <v>163</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="O2" t="s">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="P2" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="Q2" t="s">
         <v>20</v>
@@ -1554,22 +2079,22 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
         <v>49</v>
       </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" t="s">
-        <v>52</v>
-      </c>
       <c r="H3" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J3" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
@@ -1578,16 +2103,16 @@
         <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="O3" t="s">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="P3" t="s">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="Q3" t="s">
         <v>20</v>
@@ -1607,19 +2132,19 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J4" t="s">
         <v>20</v>
@@ -1631,16 +2156,16 @@
         <v>28</v>
       </c>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="O4" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="P4" t="s">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="Q4" t="s">
         <v>20</v>
@@ -1660,19 +2185,19 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -1684,16 +2209,16 @@
         <v>31</v>
       </c>
       <c r="M5" t="s">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="N5" t="s">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="O5" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="P5" t="s">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="Q5" t="s">
         <v>20</v>
@@ -1713,22 +2238,22 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" t="s">
-        <v>52</v>
-      </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J6" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -1737,16 +2262,16 @@
         <v>34</v>
       </c>
       <c r="M6" t="s">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="N6" t="s">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="O6" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="P6" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="Q6" t="s">
         <v>20</v>
@@ -1766,22 +2291,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
         <v>49</v>
       </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" t="s">
-        <v>52</v>
-      </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J7" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -1790,16 +2315,16 @@
         <v>37</v>
       </c>
       <c r="M7" t="s">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="N7" t="s">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="O7" t="s">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="P7" t="s">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="Q7" t="s">
         <v>20</v>
@@ -1819,19 +2344,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J8" t="s">
         <v>20</v>
@@ -1843,16 +2368,16 @@
         <v>40</v>
       </c>
       <c r="M8" t="s">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="N8" t="s">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="O8" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="P8" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="Q8" t="s">
         <v>20</v>
@@ -1872,19 +2397,19 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J9" t="s">
         <v>20</v>
@@ -1896,16 +2421,16 @@
         <v>43</v>
       </c>
       <c r="M9" t="s">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="N9" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="O9" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="P9" t="s">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="Q9" t="s">
         <v>20</v>
@@ -1925,19 +2450,19 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J10" t="s">
         <v>20</v>
@@ -1949,16 +2474,16 @@
         <v>46</v>
       </c>
       <c r="M10" t="s">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="N10" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="O10" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="P10" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Q10" t="s">
         <v>20</v>
@@ -1978,40 +2503,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" t="s">
         <v>49</v>
       </c>
-      <c r="E11" t="s">
+      <c r="H11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" t="s">
         <v>50</v>
       </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" t="s">
-        <v>54</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" t="s">
-        <v>55</v>
-      </c>
       <c r="M11" t="s">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="N11" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="O11" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="P11" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="Q11" t="s">
         <v>20</v>
@@ -2022,28 +2547,28 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H12" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J12" t="s">
         <v>20</v>
@@ -2052,19 +2577,19 @@
         <v>21</v>
       </c>
       <c r="L12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M12" t="s">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="N12" t="s">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="O12" t="s">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="P12" t="s">
-        <v>20</v>
+        <v>203</v>
       </c>
       <c r="Q12" t="s">
         <v>20</v>
@@ -2075,28 +2600,28 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H13" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s">
         <v>20</v>
@@ -2105,19 +2630,19 @@
         <v>21</v>
       </c>
       <c r="L13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M13" t="s">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="N13" t="s">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="O13" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="P13" t="s">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="Q13" t="s">
         <v>20</v>
@@ -2128,28 +2653,28 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s">
         <v>20</v>
@@ -2158,19 +2683,19 @@
         <v>21</v>
       </c>
       <c r="L14" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="M14" t="s">
-        <v>20</v>
+        <v>208</v>
       </c>
       <c r="N14" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
       <c r="O14" t="s">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="P14" t="s">
-        <v>20</v>
+        <v>211</v>
       </c>
       <c r="Q14" t="s">
         <v>20</v>
@@ -2181,28 +2706,28 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H15" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s">
         <v>20</v>
@@ -2211,19 +2736,19 @@
         <v>21</v>
       </c>
       <c r="L15" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="M15" t="s">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="N15" t="s">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="O15" t="s">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="P15" t="s">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="Q15" t="s">
         <v>20</v>
@@ -2234,28 +2759,28 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J16" t="s">
         <v>20</v>
@@ -2264,19 +2789,19 @@
         <v>21</v>
       </c>
       <c r="L16" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="M16" t="s">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="N16" t="s">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="O16" t="s">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="P16" t="s">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="Q16" t="s">
         <v>20</v>
@@ -2287,28 +2812,28 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H17" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J17" t="s">
         <v>20</v>
@@ -2317,19 +2842,19 @@
         <v>21</v>
       </c>
       <c r="L17" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="M17" t="s">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="N17" t="s">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="O17" t="s">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="P17" t="s">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="Q17" t="s">
         <v>20</v>
@@ -2340,28 +2865,28 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
         <v>74</v>
       </c>
-      <c r="B18" t="s">
+      <c r="E18" t="s">
         <v>75</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" t="s">
-        <v>80</v>
-      </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J18" t="s">
         <v>20</v>
@@ -2370,19 +2895,19 @@
         <v>21</v>
       </c>
       <c r="L18" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="M18" t="s">
-        <v>20</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="O18" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="P18" t="s">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="Q18" t="s">
         <v>20</v>
@@ -2393,49 +2918,49 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" t="s">
         <v>77</v>
       </c>
-      <c r="B19" t="s">
+      <c r="J19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" t="s">
         <v>78</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" t="s">
-        <v>52</v>
-      </c>
-      <c r="H19" t="s">
-        <v>82</v>
-      </c>
-      <c r="J19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" t="s">
-        <v>83</v>
-      </c>
       <c r="M19" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="N19" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="O19" t="s">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="P19" t="s">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="Q19" t="s">
         <v>20</v>
@@ -2446,49 +2971,49 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" t="s">
         <v>49</v>
       </c>
-      <c r="E20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" t="s">
-        <v>52</v>
-      </c>
       <c r="H20" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J20" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K20" t="s">
         <v>21</v>
       </c>
       <c r="L20" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="M20" t="s">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="O20" t="s">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="P20" t="s">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="Q20" t="s">
         <v>20</v>
@@ -2499,49 +3024,49 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s">
         <v>49</v>
       </c>
-      <c r="E21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" t="s">
-        <v>52</v>
-      </c>
       <c r="H21" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J21" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K21" t="s">
         <v>21</v>
       </c>
       <c r="L21" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="M21" t="s">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="N21" t="s">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="O21" t="s">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="P21" t="s">
-        <v>20</v>
+        <v>239</v>
       </c>
       <c r="Q21" t="s">
         <v>20</v>
@@ -2552,28 +3077,28 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H22" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s">
         <v>20</v>
@@ -2582,19 +3107,19 @@
         <v>21</v>
       </c>
       <c r="L22" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M22" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="N22" t="s">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="O22" t="s">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="P22" t="s">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="Q22" t="s">
         <v>20</v>
@@ -2605,28 +3130,28 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H23" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J23" t="s">
         <v>20</v>
@@ -2635,19 +3160,19 @@
         <v>21</v>
       </c>
       <c r="L23" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M23" t="s">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="O23" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="P23" t="s">
-        <v>20</v>
+        <v>247</v>
       </c>
       <c r="Q23" t="s">
         <v>20</v>
@@ -2658,49 +3183,49 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" t="s">
         <v>49</v>
       </c>
-      <c r="E24" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24" t="s">
-        <v>52</v>
-      </c>
       <c r="H24" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J24" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s">
         <v>21</v>
       </c>
       <c r="L24" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="M24" t="s">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s">
-        <v>20</v>
+        <v>249</v>
       </c>
       <c r="O24" t="s">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="P24" t="s">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="Q24" t="s">
         <v>20</v>
@@ -2711,49 +3236,49 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s">
         <v>49</v>
       </c>
-      <c r="E25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" t="s">
-        <v>52</v>
-      </c>
       <c r="H25" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J25" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s">
         <v>21</v>
       </c>
       <c r="L25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="M25" t="s">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="N25" t="s">
-        <v>20</v>
+        <v>253</v>
       </c>
       <c r="O25" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="P25" t="s">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="Q25" t="s">
         <v>20</v>
@@ -2764,49 +3289,49 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s">
         <v>49</v>
       </c>
-      <c r="E26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F26" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26" t="s">
-        <v>52</v>
-      </c>
       <c r="H26" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J26" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s">
         <v>21</v>
       </c>
       <c r="L26" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="M26" t="s">
-        <v>20</v>
+        <v>256</v>
       </c>
       <c r="N26" t="s">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="O26" t="s">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="P26" t="s">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="Q26" t="s">
         <v>20</v>
@@ -2817,28 +3342,28 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H27" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J27" t="s">
         <v>20</v>
@@ -2847,19 +3372,19 @@
         <v>21</v>
       </c>
       <c r="L27" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="M27" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="N27" t="s">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="O27" t="s">
-        <v>20</v>
+        <v>262</v>
       </c>
       <c r="P27" t="s">
-        <v>20</v>
+        <v>263</v>
       </c>
       <c r="Q27" t="s">
         <v>20</v>
@@ -2870,28 +3395,28 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H28" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J28" t="s">
         <v>20</v>
@@ -2900,19 +3425,19 @@
         <v>21</v>
       </c>
       <c r="L28" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M28" t="s">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="N28" t="s">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="O28" t="s">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="Q28" t="s">
         <v>20</v>
@@ -2923,49 +3448,49 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" t="s">
         <v>49</v>
       </c>
-      <c r="E29" t="s">
-        <v>50</v>
-      </c>
-      <c r="F29" t="s">
-        <v>51</v>
-      </c>
-      <c r="G29" t="s">
-        <v>52</v>
-      </c>
       <c r="H29" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J29" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s">
         <v>21</v>
       </c>
       <c r="L29" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="M29" t="s">
-        <v>20</v>
+        <v>268</v>
       </c>
       <c r="N29" t="s">
-        <v>20</v>
+        <v>269</v>
       </c>
       <c r="O29" t="s">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="P29" t="s">
-        <v>20</v>
+        <v>271</v>
       </c>
       <c r="Q29" t="s">
         <v>20</v>
@@ -2976,49 +3501,49 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s">
         <v>49</v>
       </c>
-      <c r="E30" t="s">
-        <v>50</v>
-      </c>
-      <c r="F30" t="s">
-        <v>51</v>
-      </c>
-      <c r="G30" t="s">
-        <v>52</v>
-      </c>
       <c r="H30" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J30" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s">
         <v>21</v>
       </c>
       <c r="L30" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="M30" t="s">
-        <v>20</v>
+        <v>272</v>
       </c>
       <c r="N30" t="s">
-        <v>20</v>
+        <v>273</v>
       </c>
       <c r="O30" t="s">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="P30" t="s">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="Q30" t="s">
         <v>20</v>
@@ -3029,28 +3554,28 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H31" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J31" t="s">
         <v>20</v>
@@ -3059,19 +3584,19 @@
         <v>21</v>
       </c>
       <c r="L31" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M31" t="s">
-        <v>20</v>
+        <v>276</v>
       </c>
       <c r="N31" t="s">
-        <v>20</v>
+        <v>277</v>
       </c>
       <c r="O31" t="s">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="P31" t="s">
-        <v>20</v>
+        <v>279</v>
       </c>
       <c r="Q31" t="s">
         <v>20</v>
@@ -3082,28 +3607,28 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G32" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J32" t="s">
         <v>20</v>
@@ -3112,19 +3637,19 @@
         <v>21</v>
       </c>
       <c r="L32" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="M32" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="N32" t="s">
-        <v>20</v>
+        <v>281</v>
       </c>
       <c r="O32" t="s">
-        <v>20</v>
+        <v>282</v>
       </c>
       <c r="P32" t="s">
-        <v>20</v>
+        <v>283</v>
       </c>
       <c r="Q32" t="s">
         <v>20</v>
@@ -3135,28 +3660,28 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H33" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J33" t="s">
         <v>20</v>
@@ -3165,19 +3690,19 @@
         <v>21</v>
       </c>
       <c r="L33" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="M33" t="s">
-        <v>20</v>
+        <v>284</v>
       </c>
       <c r="N33" t="s">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="O33" t="s">
-        <v>20</v>
+        <v>286</v>
       </c>
       <c r="P33" t="s">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="Q33" t="s">
         <v>20</v>
@@ -3188,49 +3713,49 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" t="s">
         <v>49</v>
       </c>
-      <c r="E34" t="s">
-        <v>50</v>
-      </c>
-      <c r="F34" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" t="s">
-        <v>52</v>
-      </c>
       <c r="H34" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J34" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s">
         <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="M34" t="s">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="N34" t="s">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="O34" t="s">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="P34" t="s">
-        <v>20</v>
+        <v>291</v>
       </c>
       <c r="Q34" t="s">
         <v>20</v>
@@ -3241,28 +3766,28 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H35" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J35" t="s">
         <v>20</v>
@@ -3271,19 +3796,19 @@
         <v>21</v>
       </c>
       <c r="L35" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="M35" t="s">
-        <v>20</v>
+        <v>292</v>
       </c>
       <c r="N35" t="s">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="O35" t="s">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="P35" t="s">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="Q35" t="s">
         <v>20</v>
@@ -3294,28 +3819,28 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E36" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H36" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J36" t="s">
         <v>20</v>
@@ -3324,19 +3849,19 @@
         <v>21</v>
       </c>
       <c r="L36" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="M36" t="s">
-        <v>20</v>
+        <v>296</v>
       </c>
       <c r="N36" t="s">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="O36" t="s">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="P36" t="s">
-        <v>20</v>
+        <v>299</v>
       </c>
       <c r="Q36" t="s">
         <v>20</v>
@@ -3347,49 +3872,49 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" t="s">
         <v>49</v>
       </c>
-      <c r="E37" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" t="s">
-        <v>51</v>
-      </c>
-      <c r="G37" t="s">
-        <v>52</v>
-      </c>
       <c r="H37" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J37" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s">
         <v>21</v>
       </c>
       <c r="L37" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="M37" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="N37" t="s">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="O37" t="s">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="P37" t="s">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="Q37" t="s">
         <v>20</v>
@@ -3400,28 +3925,28 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F38" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H38" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J38" t="s">
         <v>20</v>
@@ -3430,19 +3955,19 @@
         <v>21</v>
       </c>
       <c r="L38" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M38" t="s">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="N38" t="s">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="O38" t="s">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="P38" t="s">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="Q38" t="s">
         <v>20</v>
@@ -3453,28 +3978,28 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E39" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F39" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H39" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J39" t="s">
         <v>20</v>
@@ -3483,19 +4008,19 @@
         <v>21</v>
       </c>
       <c r="L39" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M39" t="s">
-        <v>20</v>
+        <v>308</v>
       </c>
       <c r="N39" t="s">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="O39" t="s">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="P39" t="s">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="Q39" t="s">
         <v>20</v>
@@ -3506,28 +4031,28 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G40" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H40" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J40" t="s">
         <v>20</v>
@@ -3536,19 +4061,19 @@
         <v>21</v>
       </c>
       <c r="L40" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M40" t="s">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="N40" t="s">
-        <v>20</v>
+        <v>313</v>
       </c>
       <c r="O40" t="s">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="P40" t="s">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="Q40" t="s">
         <v>20</v>
@@ -3559,28 +4084,28 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E41" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G41" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H41" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J41" t="s">
         <v>20</v>
@@ -3589,19 +4114,19 @@
         <v>21</v>
       </c>
       <c r="L41" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M41" t="s">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="N41" t="s">
-        <v>20</v>
+        <v>317</v>
       </c>
       <c r="O41" t="s">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="P41" t="s">
-        <v>20</v>
+        <v>319</v>
       </c>
       <c r="Q41" t="s">
         <v>20</v>
@@ -3612,28 +4137,28 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B42" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E42" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G42" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H42" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J42" t="s">
         <v>20</v>
@@ -3642,19 +4167,19 @@
         <v>21</v>
       </c>
       <c r="L42" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="M42" t="s">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="N42" t="s">
-        <v>20</v>
+        <v>321</v>
       </c>
       <c r="O42" t="s">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="P42" t="s">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="Q42" t="s">
         <v>20</v>
@@ -3665,28 +4190,28 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E43" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F43" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H43" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J43" t="s">
         <v>20</v>
@@ -3695,19 +4220,19 @@
         <v>21</v>
       </c>
       <c r="L43" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M43" t="s">
-        <v>20</v>
+        <v>324</v>
       </c>
       <c r="N43" t="s">
-        <v>20</v>
+        <v>325</v>
       </c>
       <c r="O43" t="s">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="P43" t="s">
-        <v>20</v>
+        <v>327</v>
       </c>
       <c r="Q43" t="s">
         <v>20</v>
@@ -3718,28 +4243,28 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B44" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E44" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F44" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H44" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J44" t="s">
         <v>20</v>
@@ -3748,19 +4273,19 @@
         <v>21</v>
       </c>
       <c r="L44" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="M44" t="s">
-        <v>20</v>
+        <v>328</v>
       </c>
       <c r="N44" t="s">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="O44" t="s">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="P44" t="s">
-        <v>20</v>
+        <v>331</v>
       </c>
       <c r="Q44" t="s">
         <v>20</v>
@@ -3771,49 +4296,49 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45" t="s">
+        <v>74</v>
+      </c>
+      <c r="E45" t="s">
+        <v>75</v>
+      </c>
+      <c r="F45" t="s">
+        <v>76</v>
+      </c>
+      <c r="G45" t="s">
         <v>49</v>
       </c>
-      <c r="E45" t="s">
-        <v>50</v>
-      </c>
-      <c r="F45" t="s">
-        <v>51</v>
-      </c>
-      <c r="G45" t="s">
-        <v>52</v>
-      </c>
       <c r="H45" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J45" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K45" t="s">
         <v>21</v>
       </c>
       <c r="L45" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="M45" t="s">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="N45" t="s">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="O45" t="s">
-        <v>20</v>
+        <v>334</v>
       </c>
       <c r="P45" t="s">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="Q45" t="s">
         <v>20</v>
@@ -3824,28 +4349,28 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E46" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F46" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H46" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J46" t="s">
         <v>20</v>
@@ -3854,19 +4379,19 @@
         <v>21</v>
       </c>
       <c r="L46" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M46" t="s">
-        <v>20</v>
+        <v>336</v>
       </c>
       <c r="N46" t="s">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="O46" t="s">
-        <v>20</v>
+        <v>338</v>
       </c>
       <c r="P46" t="s">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="Q46" t="s">
         <v>20</v>

--- a/DesignData/Excel_Masters/FamiliarAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/FamiliarAssets_Master.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10710"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
   </bookViews>
   <sheets>
     <sheet name="FamiliarAssets" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
     <t>/Game/External_Assets/Monster/Anemone/SKM_Anemone.SKM_Anemone</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Anemone.Icon_Anemone</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Anemone.Anemone</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Anemone/ABP_Anemone.ABP_Anemone_C'</t>
@@ -111,13 +111,16 @@
     <t>BardFollower</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_BardFollower.DA_FamiliarFX_Common_BardFollower",BasicAttackTag=(TagName="FX.Familiar.Common.BardFollower.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.BardFollower.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.BardFollower.Hit"),DeathTag=(TagName="FX.Familiar.Common.BardFollower.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/BardFollower/AM_BardFollower_BasicAttack.AM_BardFollower_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/BardFollower/SKM_BardFollower.SKM_BardFollower</t>
   </si>
   <si>
-    <t>/Game/UI/Img/Img_Unit/?좊떅1.?좊떅1</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/BardFollower.BardFollower</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/BardFollower/ABP_BardFollower.ABP_BardFollower_C'</t>
@@ -132,16 +135,19 @@
     <t>Bat</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Bat.DA_FamiliarFX_Common_Bat",BasicAttackTag=(TagName="FX.Familiar.Common.Bat.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Bat.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Bat.Hit"),DeathTag=(TagName="FX.Familiar.Common.Bat.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Bat/AM_Bat_BasicAttack.AM_Bat_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Bat/SKM_Bat.SKM_Bat</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Bat.Icon_Bat</t>
-  </si>
-  <si>
-    <t>None</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Boss_Bat.Icon_Boss_Bat</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Bat/ABP_Bat.ABP_Bat_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Bat/AM_Bat_Damaged.AM_Bat_Damaged</t>
@@ -153,6 +159,9 @@
     <t>Cannon</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Cannon.DA_FamiliarFX_Common_Cannon",BasicAttackTag=(TagName="FX.Familiar.Common.Cannon.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Cannon.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Cannon.Hit"),DeathTag=(TagName="FX.Familiar.Common.Cannon.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Cannon/AM_Cannon_BasicAttack.AM_Cannon_BasicAttack</t>
   </si>
   <si>
@@ -162,7 +171,10 @@
     <t>/Game/External_Assets/Monster/Cannon/SKM_Cannon.SKM_Cannon</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Cannon.Icon_Cannon</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Boss_Cannon.Icon_Boss_Cannon</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Cannon/ABP_Cannon.ABP_Cannon_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Cannon/AM_Cannon_Damaged.AM_Cannon_Damaged</t>
@@ -174,6 +186,9 @@
     <t>CherryBee</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_CherryBee.DA_FamiliarFX_Common_CherryBee",BasicAttackTag=(TagName="FX.Familiar.Common.CherryBee.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.CherryBee.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.CherryBee.Hit"),DeathTag=(TagName="FX.Familiar.Common.CherryBee.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/CherryBee/AM_CherryBee_BasicAttack.AM_CherryBee_BasicAttack</t>
   </si>
   <si>
@@ -183,7 +198,7 @@
     <t>/Game/External_Assets/Monster/CherryBee/SKM_CherryBee.SKM_CherryBee</t>
   </si>
   <si>
-    <t>/Game/UI/Img/Img_Unit/?좊떅2.?좊떅2</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/CherryBee.CherryBee</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/CherryBee/ABP_CherryBee.ABP_CherryBee_C'</t>
@@ -198,13 +213,19 @@
     <t>Clownfish</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Clownfish.DA_FamiliarFX_Common_Clownfish",BasicAttackTag=(TagName="FX.Familiar.Common.Clownfish.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Clownfish.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Clownfish.Hit"),DeathTag=(TagName="FX.Familiar.Common.Clownfish.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Clownfish/AM_Clownfish_BasicAttack.AM_Clownfish_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Clownfish/SKM_Clownfish.SKM_Clownfish</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Clownfish.Icon_Clownfish</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Clownfish.Clownfish</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Clownfish/ABP_Clownfish.ABP_Clownfish_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Clownfish/AM_Clownfish_Damaged.AM_Clownfish_Damaged</t>
@@ -216,13 +237,19 @@
     <t>CowardTurtle</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_CowardTurtle.DA_FamiliarFX_Common_CowardTurtle",BasicAttackTag=(TagName="FX.Familiar.Common.CowardTurtle.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.CowardTurtle.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.CowardTurtle.Hit"),DeathTag=(TagName="FX.Familiar.Common.CowardTurtle.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/CowardTurtle/AM_CowardTurtle_BasicAttack.AM_CowardTurtle_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/CowardTurtle/SKM_CowardTurtle.SKM_CowardTurtle</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_CowardTurtle.Icon_CowardTurtle</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/CowardTurtle.CowardTurtle</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/CowardTurtle/ABP_CowardTurtle.ABP_CowardTurtle_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/CowardTurtle/AM_CowardTurtle_Damaged.AM_CowardTurtle_Damaged</t>
@@ -234,13 +261,16 @@
     <t>CupFelice</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_CupFelice.DA_FamiliarFX_Common_CupFelice",BasicAttackTag=(TagName="FX.Familiar.Common.CupFelice.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.CupFelice.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.CupFelice.Hit"),DeathTag=(TagName="FX.Familiar.Common.CupFelice.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/CupFelice/AM_CupFelice_BasicAttack.AM_CupFelice_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/CupFelice/SKM_CupFelice.SKM_CupFelice</t>
   </si>
   <si>
-    <t>/Game/UI/Img/Img_Unit/?좊떅3.?좊떅3</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/CupFelice.CupFelice</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/CupFelice/ABP_CupFelice.ABP_CupFelice_C'</t>
@@ -255,13 +285,16 @@
     <t>DarumaNeko</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_DarumaNeko.DA_FamiliarFX_Common_DarumaNeko",BasicAttackTag=(TagName="FX.Familiar.Common.DarumaNeko.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.DarumaNeko.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.DarumaNeko.Hit"),DeathTag=(TagName="FX.Familiar.Common.DarumaNeko.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/DarumaNeko/AM_DarumaNeko_BasicAttack.AM_DarumaNeko_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/DarumaNeko/SKM_DarumaNeko.SKM_DarumaNeko</t>
   </si>
   <si>
-    <t>/Game/UI/Img/Img_Unit/?좊떅5.?좊떅5</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DarumaNeko.Icon_DarumaNeko</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/DarumaNeko/ABP_DarumaNeko.ABP_DarumaNeko_C'</t>
@@ -276,13 +309,19 @@
     <t>FanOfDeath</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_FanOfDeath.DA_FamiliarFX_Common_FanOfDeath",BasicAttackTag=(TagName="FX.Familiar.Common.FanOfDeath.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.FanOfDeath.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.FanOfDeath.Hit"),DeathTag=(TagName="FX.Familiar.Common.FanOfDeath.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/FanOfDeath/AM_FanOfDeath_BasicAttack.AM_FanOfDeath_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/FanOfDeath/SKM_FanOfDeath.SKM_FanOfDeath</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FanOfDeath.Icon_FanOfDeath</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/FanOfDeath.FanOfDeath</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/FanOfDeath/ABP_FanOfDeath.ABP_FanOfDeath_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/FanOfDeath/AM_FanOfDeath_Damaged.AM_FanOfDeath_Damaged</t>
@@ -294,6 +333,9 @@
     <t>Felice</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Felice.DA_FamiliarFX_Common_Felice",BasicAttackTag=(TagName="FX.Familiar.Common.Felice.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Felice.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Felice.Hit"),DeathTag=(TagName="FX.Familiar.Common.Felice.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Felice/AM_Felice_BasicAttack.AM_Felice_BasicAttack</t>
   </si>
   <si>
@@ -315,13 +357,19 @@
     <t>Felicis</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Felicis.DA_FamiliarFX_Common_Felicis",BasicAttackTag=(TagName="FX.Familiar.Common.Felicis.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Felicis.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Felicis.Hit"),DeathTag=(TagName="FX.Familiar.Common.Felicis.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Felicis/AM_Felicis_BasicAttack.AM_Felicis_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Felicis/SKM_Felicis.SKM_Felicis</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Felicis.Icon_Felicis</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Felicis.Felicis</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Felicis/ABP_Felicis.ABP_Felicis_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Felicis/AM_Felicis_Damaged.AM_Felicis_Damaged</t>
@@ -333,13 +381,19 @@
     <t>FelicisGuard</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_FelicisGuard.DA_FamiliarFX_Common_FelicisGuard",BasicAttackTag=(TagName="FX.Familiar.Common.FelicisGuard.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.FelicisGuard.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.FelicisGuard.Hit"),DeathTag=(TagName="FX.Familiar.Common.FelicisGuard.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/FelicisGuard/AM_FelicisGuard_BasicAttack.AM_FelicisGuard_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/FelicisGuard/SKM_FelicisGuard.SKM_FelicisGuard</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FelicisGuard.Icon_FelicisGuard</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/FelicisGuard.FelicisGuard</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/FelicisGuard/ABP_FelicisGuard.ABP_FelicisGuard_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/FelicisGuard/AM_FelicisGuard_Damaged.AM_FelicisGuard_Damaged</t>
@@ -351,13 +405,16 @@
     <t>Firefly</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Firefly.DA_FamiliarFX_Common_Firefly",BasicAttackTag=(TagName="FX.Familiar.Common.Firefly.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Firefly.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Firefly.Hit"),DeathTag=(TagName="FX.Familiar.Common.Firefly.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Firefly/AM_Firefly_BasicAttack.AM_Firefly_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Firefly/SKM_Firefly.SKM_Firefly</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Firefly.Icon_Firefly</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Firefly.Firefly</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Firefly/ABP_Firefly.ABP_Firefly_C'</t>
@@ -372,13 +429,19 @@
     <t>Fly</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Fly.DA_FamiliarFX_Common_Fly",BasicAttackTag=(TagName="FX.Familiar.Common.Fly.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Fly.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Fly.Hit"),DeathTag=(TagName="FX.Familiar.Common.Fly.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Fly/AM_Fly_BasicAttack.AM_Fly_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Fly/SKM_Fly.SKM_Fly</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Fly.Icon_Fly</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Fly.Fly</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Fly/ABP_Fly.ABP_Fly_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Fly/AM_Fly_Damaged.AM_Fly_Damaged</t>
@@ -390,12 +453,18 @@
     <t>ForestMacaron</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_ForestMacaron.DA_FamiliarFX_Common_ForestMacaron",BasicAttackTag=(TagName="FX.Familiar.Common.ForestMacaron.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.ForestMacaron.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.ForestMacaron.Hit"),DeathTag=(TagName="FX.Familiar.Common.ForestMacaron.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/ForestMacaron/AM_ForestMacarom_BasicAttack.AM_ForestMacarom_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/ForestMacaron/SKM_ForestMacaron.SKM_ForestMacaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/ForestMacaron.ForestMacaron</t>
+  </si>
+  <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/ForestMacaron/ABP_ForestMacaron.ABP_ForestMacaron_C'</t>
   </si>
   <si>
@@ -408,13 +477,16 @@
     <t>ForestSpirit</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_ForestSpirit.DA_FamiliarFX_Common_ForestSpirit",BasicAttackTag=(TagName="FX.Familiar.Common.ForestSpirit.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.ForestSpirit.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.ForestSpirit.Hit"),DeathTag=(TagName="FX.Familiar.Common.ForestSpirit.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/ForestSpirit/AM_ForestSpirit_BasicAttack.AM_ForestSpirit_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/ForestSpirit/SKM_ForestSpirit.SKM_ForestSpirit</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Icon/Icon_ProfileFrame/Icon_Forest_Frame.Icon_Forest_Frame</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/ForestSpirit.ForestSpirit</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/ForestSpirit/ABP_ForestSpirit.ABP_ForestSpirit_C'</t>
@@ -429,6 +501,9 @@
     <t>Foxhound</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Foxhound.DA_FamiliarFX_Common_Foxhound",BasicAttackTag=(TagName="FX.Familiar.Common.Foxhound.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Foxhound.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Foxhound.Hit"),DeathTag=(TagName="FX.Familiar.Common.Foxhound.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Attack.AM_Foxhound_Attack</t>
   </si>
   <si>
@@ -441,6 +516,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FoxHound.Icon_FoxHound</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Foxhound/ABP_Foxhound.ABP_Foxhound_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Damage.AM_Foxhound_Damage</t>
   </si>
   <si>
@@ -450,13 +528,19 @@
     <t>GoldMacaron</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_GoldMacaron.DA_FamiliarFX_Common_GoldMacaron",BasicAttackTag=(TagName="FX.Familiar.Common.GoldMacaron.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.GoldMacaron.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.GoldMacaron.Hit"),DeathTag=(TagName="FX.Familiar.Common.GoldMacaron.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/GoldMacaron/AM_GoldMacaron_BasicAttack.AM_GoldMacaron_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/GoldMacaron/SKM_Gold_Macaron.SKM_Gold_Macaron</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GoldMacaron.Icon_GoldMacaron</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/GoldMacaron.GoldMacaron</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/GoldMacaron/ABP_GoldMacaron.ABP_GoldMacaron_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/GoldMacaron/AM_GoldMacaron_Damaged.AM_GoldMacaron_Damaged</t>
@@ -468,6 +552,9 @@
     <t>Golem</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Golem.DA_FamiliarFX_Common_Golem",BasicAttackTag=(TagName="FX.Familiar.Common.Golem.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Golem.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Golem.Hit"),DeathTag=(TagName="FX.Familiar.Common.Golem.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Golem/AM_Golem_BasicAttack.AM_Golem_BasicAttack</t>
   </si>
   <si>
@@ -477,6 +564,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Golem.Icon_Golem</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Golem/ABP_Golem.ABP_Golem_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Golem/AM_Golem_Damaged.AM_Golem_Damaged</t>
   </si>
   <si>
@@ -486,13 +576,19 @@
     <t>GuardianTreantMini</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_GuardianTreantMini.DA_FamiliarFX_Common_GuardianTreantMini",BasicAttackTag=(TagName="FX.Familiar.Common.GuardianTreantMini.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.GuardianTreantMini.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.GuardianTreantMini.Hit"),DeathTag=(TagName="FX.Familiar.Common.GuardianTreantMini.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/GuardianTreantMini/AM_GuardianTreantMini_BasicAttack.AM_GuardianTreantMini_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/GuardianTreantMini/SKM_GuardianTreantMini.SKM_GuardianTreantMini</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GuardianTreantMini.Icon_GuardianTreantMini</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/GuardianTreantMini.GuardianTreantMini</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/GuardianTreantMini/ABP_GuardianTreantMini.ABP_GuardianTreantMini_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/GuardianTreantMini/AM_GuardianTreantMini_Damaged.AM_GuardianTreantMini_Damaged</t>
@@ -504,13 +600,19 @@
     <t>Imp</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Imp.DA_FamiliarFX_Common_Imp",BasicAttackTag=(TagName="FX.Familiar.Common.Imp.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Imp.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Imp.Hit"),DeathTag=(TagName="FX.Familiar.Common.Imp.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Imp/AM_Imp_BasicAttack.AM_Imp_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Imp/SKM_Imp.SKM_Imp</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Imp.Icon_Imp</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Imp.Imp</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Imp/ABP_Imp.ABP_Imp_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Imp/AM_Imp_Damaged.AM_Imp_Damaged</t>
@@ -522,13 +624,19 @@
     <t>Leech</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Leech.DA_FamiliarFX_Common_Leech",BasicAttackTag=(TagName="FX.Familiar.Common.Leech.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Leech.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Leech.Hit"),DeathTag=(TagName="FX.Familiar.Common.Leech.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Leech/AM_Leech_BasicAttack.AM_Leech_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Leech/SKM_Leech.SKM_Leech</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Leech.Icon_Leech</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Boss_Leech_D.Icon_Boss_Leech_D</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Leech/ABP_Leech.ABP_Leech_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Leech/AM_Leech_Damaged.AM_Leech_Damaged</t>
@@ -540,13 +648,19 @@
     <t>Macaron</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Macaron.DA_FamiliarFX_Common_Macaron",BasicAttackTag=(TagName="FX.Familiar.Common.Macaron.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Macaron.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Macaron.Hit"),DeathTag=(TagName="FX.Familiar.Common.Macaron.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Macaron/AM_Macaron_BasicAttack.AM_Macaron_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Macaron/SKM_Macaron.SKM_Macaron</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Macaron.Icon_Macaron</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Macaron.Macaron</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Macaron/ABP_Macaron.ABP_Macaron_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Macaron/AM_Macaron_Damaged.AM_Macaron_Damaged</t>
@@ -558,13 +672,19 @@
     <t>MageMacaron</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_MageMacaron.DA_FamiliarFX_Common_MageMacaron",BasicAttackTag=(TagName="FX.Familiar.Common.MageMacaron.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.MageMacaron.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.MageMacaron.Hit"),DeathTag=(TagName="FX.Familiar.Common.MageMacaron.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/MageMacaron/AM_MageMacaron_BasicAttack.AM_MageMacaron_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/MageMacaron/SKM_MageMacaron.SKM_MageMacaron</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MageMacaron.Icon_MageMacaron</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/MageMacaron.MageMacaron</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MageMacaron/ABP_MageMacaron.ABP_MageMacaron_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/MageMacaron/AM_MageMacaron_Damaged.AM_MageMacaron_Damaged</t>
@@ -576,6 +696,9 @@
     <t>MagicPot</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_MagicPot.DA_FamiliarFX_Common_MagicPot",BasicAttackTag=(TagName="FX.Familiar.Common.MagicPot.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.MagicPot.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.MagicPot.Hit"),DeathTag=(TagName="FX.Familiar.Common.MagicPot.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/MagicPot/AM_MagicPot_BasicAttack.AM_MagicPot_BasicAttack</t>
   </si>
   <si>
@@ -585,6 +708,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MagicPot.Icon_MagicPot</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MagicPot/ABP_MagicPot.ABP_MagicPot_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/MagicPot/AM_MagicPot_Damaged.AM_MagicPot_Damaged</t>
   </si>
   <si>
@@ -594,13 +720,19 @@
     <t>Messenger</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Messenger.DA_FamiliarFX_Common_Messenger",BasicAttackTag=(TagName="FX.Familiar.Common.Messenger.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Messenger.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Messenger.Hit"),DeathTag=(TagName="FX.Familiar.Common.Messenger.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Messenger/AM_Messenger_BasicAttack.AM_Messenger_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Messenger/SKM_Messenger.SKM_Messenger</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Messenger.Icon_Messenger</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Messenger.Messenger</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Messenger/ABP_Messenger.ABP_Messenger_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Messenger/AM_Messenger_Damaged.AM_Messenger_Damaged</t>
@@ -612,13 +744,19 @@
     <t>MinimiNeko</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_MinimiNeko.DA_FamiliarFX_Common_MinimiNeko",BasicAttackTag=(TagName="FX.Familiar.Common.MinimiNeko.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.MinimiNeko.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.MinimiNeko.Hit"),DeathTag=(TagName="FX.Familiar.Common.MinimiNeko.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/MinimiNeko/AM_MinimiNeko_BasicAttack.AM_MinimiNeko_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/MinimiNeko/SKM_MinimiNeko.SKM_MinimiNeko</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MinimiNeko.Icon_MinimiNeko</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/MinimiNeko.MinimiNeko</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MinimiNeko/ABP_MinimiNeko.ABP_MinimiNeko_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/MinimiNeko/AM_MinimiNeko_Damaged.AM_MinimiNeko_Damaged</t>
@@ -630,13 +768,19 @@
     <t>MummyMacaron</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_MummyMacaron.DA_FamiliarFX_Common_MummyMacaron",BasicAttackTag=(TagName="FX.Familiar.Common.MummyMacaron.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.MummyMacaron.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.MummyMacaron.Hit"),DeathTag=(TagName="FX.Familiar.Common.MummyMacaron.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/MummyMacaron/AM_MummyMacaron_BasicAttack.AM_MummyMacaron_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/MummyMacaron/SKM_MummyMacaron_A.SKM_MummyMacaron_A</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MummyMacaron.Icon_MummyMacaron</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/MummyMacaron.MummyMacaron</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MummyMacaron/ABP_MummyMacaron.ABP_MummyMacaron_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/MummyMacaron/AM_MummyMacaron_Damaged.AM_MummyMacaron_Damaged</t>
@@ -648,13 +792,19 @@
     <t>Mushroom</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Mushroom.DA_FamiliarFX_Common_Mushroom",BasicAttackTag=(TagName="FX.Familiar.Common.Mushroom.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Mushroom.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Mushroom.Hit"),DeathTag=(TagName="FX.Familiar.Common.Mushroom.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Mushroom/AM_Mushroom_BasicAttack.AM_Mushroom_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Mushroom/SKM_Mushroom_A.SKM_Mushroom_A</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mushroom.Icon_Mushroom</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Mushroom.Mushroom</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Mushroom/ABP_Mushroom.ABP_Mushroom_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Mushroom/AM_Mushroom_Damaged.AM_Mushroom_Damaged</t>
@@ -666,13 +816,19 @@
     <t>NetherConnector</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_NetherConnector.DA_FamiliarFX_Common_NetherConnector",BasicAttackTag=(TagName="FX.Familiar.Common.NetherConnector.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.NetherConnector.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.NetherConnector.Hit"),DeathTag=(TagName="FX.Familiar.Common.NetherConnector.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/NetherConnector/AM_NetherConnector_BasicAttack.AM_NetherConnector_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/NetherConnector/SKM_NetherConnector.SKM_NetherConnector</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_NetherConnector.Icon_NetherConnector</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/NetherConnector.NetherConnector</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/NetherConnector/ABP_NetherConnector.ABP_NetherConnector_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/NetherConnector/AM_NetherConnector_Damaged.AM_NetherConnector_Damaged</t>
@@ -684,6 +840,9 @@
     <t>Oowl</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Oowl.DA_FamiliarFX_Common_Oowl",BasicAttackTag=(TagName="FX.Familiar.Common.Oowl.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Oowl.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Oowl.Hit"),DeathTag=(TagName="FX.Familiar.Common.Oowl.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Oowl/AM_Oowl_BasicAttack.AM_Oowl_BasicAttack</t>
   </si>
   <si>
@@ -693,6 +852,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Oowl.Icon_Oowl</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Oowl/ABP_Oowl.ABP_Oowl_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Oowl/AM_Oowl_Damaged.AM_Oowl_Damaged</t>
   </si>
   <si>
@@ -702,13 +864,19 @@
     <t>SmashingShrimp</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_SmashingShrimp.DA_FamiliarFX_Common_SmashingShrimp",BasicAttackTag=(TagName="FX.Familiar.Common.SmashingShrimp.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.SmashingShrimp.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.SmashingShrimp.Hit"),DeathTag=(TagName="FX.Familiar.Common.SmashingShrimp.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/SmashingShrimp/AM_SmashingShrimp_BasicAttack.AM_SmashingShrimp_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/SmashingShrimp/SKM_SmashingShrimp.SKM_SmashingShrimp</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_SmashingShrimp.Icon_SmashingShrimp</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/SmashingShrimp.SmashingShrimp</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/SmashingShrimp/ABP_SmashingShrimp.ABP_SmashingShrimp_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/SmashingShrimp/AM_SmashingShrimp_Damaged.AM_SmashingShrimp_Damaged</t>
@@ -720,13 +888,19 @@
     <t>Tacodora</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Tacodora.DA_FamiliarFX_Common_Tacodora",BasicAttackTag=(TagName="FX.Familiar.Common.Tacodora.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Tacodora.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Tacodora.Hit"),DeathTag=(TagName="FX.Familiar.Common.Tacodora.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Tacodora/AM_Tacodora_BasicAttack.AM_Tacodora_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Tacodora/SKM_takodora.SKM_takodora</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Tacodora.Icon_Tacodora</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Tacodora.Tacodora</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Tacodora/ABP_Tacodora.ABP_Tacodora_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Tacodora/AM_Tacodora_Damaged.AM_Tacodora_Damaged</t>
@@ -738,13 +912,19 @@
     <t>Trumduck</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Trumduck.DA_FamiliarFX_Common_Trumduck",BasicAttackTag=(TagName="FX.Familiar.Common.Trumduck.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Trumduck.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Trumduck.Hit"),DeathTag=(TagName="FX.Familiar.Common.Trumduck.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/TrumDuck/AM_Trumduck_BasicAttack.AM_Trumduck_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Trumduck/SKM_Trumduck.SKM_Trumduck</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Trumduck.Icon_Trumduck</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Boss_Trumduck_B.Icon_Boss_Trumduck_B</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/TrumDuck/ABP_TrumDuck.ABP_TrumDuck_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/TrumDuck/AM_Trumduck_Damaged.AM_Trumduck_Damaged</t>
@@ -756,6 +936,9 @@
     <t>Turret</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Turret.DA_FamiliarFX_Common_Turret",BasicAttackTag=(TagName="FX.Familiar.Common.Turret.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Turret.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Turret.Hit"),DeathTag=(TagName="FX.Familiar.Common.Turret.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Turret/AM_Turret_BasicAttack.AM_Turret_BasicAttack</t>
   </si>
   <si>
@@ -765,6 +948,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Turret.Icon_Turret</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Turret/ABP_Turret.ABP_Turret_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Turret/AM_Turret_Damaged.AM_Turret_Damaged</t>
   </si>
   <si>
@@ -774,13 +960,19 @@
     <t>Turtlog</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Turtlog.DA_FamiliarFX_Common_Turtlog",BasicAttackTag=(TagName="FX.Familiar.Common.Turtlog.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Turtlog.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Turtlog.Hit"),DeathTag=(TagName="FX.Familiar.Common.Turtlog.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Turtlog/AM_Turtlog_BasicAttack.AM_Turtlog_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Turtlog/SKM_Turtlog.SKM_Turtlog</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Turtlog.Icon_Turtlog</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Boss_Turtlog.Icon_Boss_Turtlog</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Turtlog/ABP_Turtlog.ABP_Turtlog_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Turtlog/AM_Turtlog_Damaged.AM_Turtlog_Damaged</t>
@@ -792,224 +984,32 @@
     <t>Usami</t>
   </si>
   <si>
+    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Usami.DA_FamiliarFX_Common_Usami",BasicAttackTag=(TagName="FX.Familiar.Common.Usami.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Usami.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Usami.Hit"),DeathTag=(TagName="FX.Familiar.Common.Usami.Death"))</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Familiar/Usami/AM_Usami_BasicAttack.AM_Usami_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Usami/SKM_Usami.SKM_Usami</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Usami.Icon_Usami</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Usami.Usami</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Usami/ABP_Usami.ABP_Usami_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Usami/AM_Usami_Damaged.AM_Usami_Damaged</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/Usami/AM_Usami_Dead.AM_Usami_Dead</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Bat/ABP_Bat.ABP_Bat_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Cannon/ABP_Cannon.ABP_Cannon_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Clownfish/ABP_Clownfish.ABP_Clownfish_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/CowardTurtle/ABP_CowardTurtle.ABP_CowardTurtle_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/FanOfDeath/ABP_FanOfDeath.ABP_FanOfDeath_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Felicis/ABP_Felicis.ABP_Felicis_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/FelicisGuard/ABP_FelicisGuard.ABP_FelicisGuard_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Fly/ABP_Fly.ABP_Fly_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Foxhound/ABP_Foxhound.ABP_Foxhound_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/GoldMacaron/ABP_GoldMacaron.ABP_GoldMacaron_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Golem/ABP_Golem.ABP_Golem_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/GuardianTreantMini/ABP_GuardianTreantMini.ABP_GuardianTreantMini_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Imp/ABP_Imp.ABP_Imp_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Leech/ABP_Leech.ABP_Leech_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Macaron/ABP_Macaron.ABP_Macaron_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MageMacaron/ABP_MageMacaron.ABP_MageMacaron_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MagicPot/ABP_MagicPot.ABP_MagicPot_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Messenger/ABP_Messenger.ABP_Messenger_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MinimiNeko/ABP_MinimiNeko.ABP_MinimiNeko_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/MummyMacaron/ABP_MummyMacaron.ABP_MummyMacaron_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Mushroom/ABP_Mushroom.ABP_Mushroom_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/NetherConnector/ABP_NetherConnector.ABP_NetherConnector_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Oowl/ABP_Oowl.ABP_Oowl_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/SmashingShrimp/ABP_SmashingShrimp.ABP_SmashingShrimp_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Tacodora/ABP_Tacodora.ABP_Tacodora_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Trumduck/ABP_Trumduck.ABP_Trumduck_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Turret/ABP_Turret.ABP_Turret_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Turtlog/ABP_Turtlog.ABP_Turtlog_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Usami/ABP_Usami.ABP_Usami_C'</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_BardFollower.DA_FamiliarFX_Common_BardFollower",BasicAttackTag=(TagName="FX.Familiar.Common.BardFollower.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.BardFollower.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.BardFollower.Hit"),DeathTag=(TagName="FX.Familiar.Common.BardFollower.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Bat.DA_FamiliarFX_Common_Bat",BasicAttackTag=(TagName="FX.Familiar.Common.Bat.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Bat.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Bat.Hit"),DeathTag=(TagName="FX.Familiar.Common.Bat.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Cannon.DA_FamiliarFX_Common_Cannon",BasicAttackTag=(TagName="FX.Familiar.Common.Cannon.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Cannon.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Cannon.Hit"),DeathTag=(TagName="FX.Familiar.Common.Cannon.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_CherryBee.DA_FamiliarFX_Common_CherryBee",BasicAttackTag=(TagName="FX.Familiar.Common.CherryBee.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.CherryBee.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.CherryBee.Hit"),DeathTag=(TagName="FX.Familiar.Common.CherryBee.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Clownfish.DA_FamiliarFX_Common_Clownfish",BasicAttackTag=(TagName="FX.Familiar.Common.Clownfish.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Clownfish.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Clownfish.Hit"),DeathTag=(TagName="FX.Familiar.Common.Clownfish.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_CowardTurtle.DA_FamiliarFX_Common_CowardTurtle",BasicAttackTag=(TagName="FX.Familiar.Common.CowardTurtle.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.CowardTurtle.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.CowardTurtle.Hit"),DeathTag=(TagName="FX.Familiar.Common.CowardTurtle.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_CupFelice.DA_FamiliarFX_Common_CupFelice",BasicAttackTag=(TagName="FX.Familiar.Common.CupFelice.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.CupFelice.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.CupFelice.Hit"),DeathTag=(TagName="FX.Familiar.Common.CupFelice.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_DarumaNeko.DA_FamiliarFX_Common_DarumaNeko",BasicAttackTag=(TagName="FX.Familiar.Common.DarumaNeko.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.DarumaNeko.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.DarumaNeko.Hit"),DeathTag=(TagName="FX.Familiar.Common.DarumaNeko.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_FanOfDeath.DA_FamiliarFX_Common_FanOfDeath",BasicAttackTag=(TagName="FX.Familiar.Common.FanOfDeath.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.FanOfDeath.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.FanOfDeath.Hit"),DeathTag=(TagName="FX.Familiar.Common.FanOfDeath.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Felice.DA_FamiliarFX_Common_Felice",BasicAttackTag=(TagName="FX.Familiar.Common.Felice.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Felice.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Felice.Hit"),DeathTag=(TagName="FX.Familiar.Common.Felice.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Felicis.DA_FamiliarFX_Common_Felicis",BasicAttackTag=(TagName="FX.Familiar.Common.Felicis.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Felicis.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Felicis.Hit"),DeathTag=(TagName="FX.Familiar.Common.Felicis.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_FelicisGuard.DA_FamiliarFX_Common_FelicisGuard",BasicAttackTag=(TagName="FX.Familiar.Common.FelicisGuard.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.FelicisGuard.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.FelicisGuard.Hit"),DeathTag=(TagName="FX.Familiar.Common.FelicisGuard.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Firefly.DA_FamiliarFX_Common_Firefly",BasicAttackTag=(TagName="FX.Familiar.Common.Firefly.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Firefly.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Firefly.Hit"),DeathTag=(TagName="FX.Familiar.Common.Firefly.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Fly.DA_FamiliarFX_Common_Fly",BasicAttackTag=(TagName="FX.Familiar.Common.Fly.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Fly.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Fly.Hit"),DeathTag=(TagName="FX.Familiar.Common.Fly.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_ForestMacaron.DA_FamiliarFX_Common_ForestMacaron",BasicAttackTag=(TagName="FX.Familiar.Common.ForestMacaron.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.ForestMacaron.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.ForestMacaron.Hit"),DeathTag=(TagName="FX.Familiar.Common.ForestMacaron.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_ForestSpirit.DA_FamiliarFX_Common_ForestSpirit",BasicAttackTag=(TagName="FX.Familiar.Common.ForestSpirit.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.ForestSpirit.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.ForestSpirit.Hit"),DeathTag=(TagName="FX.Familiar.Common.ForestSpirit.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Foxhound.DA_FamiliarFX_Common_Foxhound",BasicAttackTag=(TagName="FX.Familiar.Common.Foxhound.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Foxhound.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Foxhound.Hit"),DeathTag=(TagName="FX.Familiar.Common.Foxhound.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_GoldMacaron.DA_FamiliarFX_Common_GoldMacaron",BasicAttackTag=(TagName="FX.Familiar.Common.GoldMacaron.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.GoldMacaron.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.GoldMacaron.Hit"),DeathTag=(TagName="FX.Familiar.Common.GoldMacaron.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Golem.DA_FamiliarFX_Common_Golem",BasicAttackTag=(TagName="FX.Familiar.Common.Golem.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Golem.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Golem.Hit"),DeathTag=(TagName="FX.Familiar.Common.Golem.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_GuardianTreantMini.DA_FamiliarFX_Common_GuardianTreantMini",BasicAttackTag=(TagName="FX.Familiar.Common.GuardianTreantMini.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.GuardianTreantMini.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.GuardianTreantMini.Hit"),DeathTag=(TagName="FX.Familiar.Common.GuardianTreantMini.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Imp.DA_FamiliarFX_Common_Imp",BasicAttackTag=(TagName="FX.Familiar.Common.Imp.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Imp.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Imp.Hit"),DeathTag=(TagName="FX.Familiar.Common.Imp.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Leech.DA_FamiliarFX_Common_Leech",BasicAttackTag=(TagName="FX.Familiar.Common.Leech.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Leech.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Leech.Hit"),DeathTag=(TagName="FX.Familiar.Common.Leech.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Macaron.DA_FamiliarFX_Common_Macaron",BasicAttackTag=(TagName="FX.Familiar.Common.Macaron.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Macaron.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Macaron.Hit"),DeathTag=(TagName="FX.Familiar.Common.Macaron.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_MageMacaron.DA_FamiliarFX_Common_MageMacaron",BasicAttackTag=(TagName="FX.Familiar.Common.MageMacaron.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.MageMacaron.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.MageMacaron.Hit"),DeathTag=(TagName="FX.Familiar.Common.MageMacaron.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_MagicPot.DA_FamiliarFX_Common_MagicPot",BasicAttackTag=(TagName="FX.Familiar.Common.MagicPot.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.MagicPot.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.MagicPot.Hit"),DeathTag=(TagName="FX.Familiar.Common.MagicPot.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Messenger.DA_FamiliarFX_Common_Messenger",BasicAttackTag=(TagName="FX.Familiar.Common.Messenger.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Messenger.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Messenger.Hit"),DeathTag=(TagName="FX.Familiar.Common.Messenger.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_MinimiNeko.DA_FamiliarFX_Common_MinimiNeko",BasicAttackTag=(TagName="FX.Familiar.Common.MinimiNeko.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.MinimiNeko.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.MinimiNeko.Hit"),DeathTag=(TagName="FX.Familiar.Common.MinimiNeko.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_MummyMacaron.DA_FamiliarFX_Common_MummyMacaron",BasicAttackTag=(TagName="FX.Familiar.Common.MummyMacaron.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.MummyMacaron.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.MummyMacaron.Hit"),DeathTag=(TagName="FX.Familiar.Common.MummyMacaron.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Mushroom.DA_FamiliarFX_Common_Mushroom",BasicAttackTag=(TagName="FX.Familiar.Common.Mushroom.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Mushroom.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Mushroom.Hit"),DeathTag=(TagName="FX.Familiar.Common.Mushroom.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_NetherConnector.DA_FamiliarFX_Common_NetherConnector",BasicAttackTag=(TagName="FX.Familiar.Common.NetherConnector.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.NetherConnector.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.NetherConnector.Hit"),DeathTag=(TagName="FX.Familiar.Common.NetherConnector.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Oowl.DA_FamiliarFX_Common_Oowl",BasicAttackTag=(TagName="FX.Familiar.Common.Oowl.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Oowl.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Oowl.Hit"),DeathTag=(TagName="FX.Familiar.Common.Oowl.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_SmashingShrimp.DA_FamiliarFX_Common_SmashingShrimp",BasicAttackTag=(TagName="FX.Familiar.Common.SmashingShrimp.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.SmashingShrimp.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.SmashingShrimp.Hit"),DeathTag=(TagName="FX.Familiar.Common.SmashingShrimp.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Tacodora.DA_FamiliarFX_Common_Tacodora",BasicAttackTag=(TagName="FX.Familiar.Common.Tacodora.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Tacodora.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Tacodora.Hit"),DeathTag=(TagName="FX.Familiar.Common.Tacodora.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Trumduck.DA_FamiliarFX_Common_Trumduck",BasicAttackTag=(TagName="FX.Familiar.Common.Trumduck.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Trumduck.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Trumduck.Hit"),DeathTag=(TagName="FX.Familiar.Common.Trumduck.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Turret.DA_FamiliarFX_Common_Turret",BasicAttackTag=(TagName="FX.Familiar.Common.Turret.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Turret.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Turret.Hit"),DeathTag=(TagName="FX.Familiar.Common.Turret.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Turtlog.DA_FamiliarFX_Common_Turtlog",BasicAttackTag=(TagName="FX.Familiar.Common.Turtlog.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Turtlog.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Turtlog.Hit"),DeathTag=(TagName="FX.Familiar.Common.Turtlog.Death"))</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Usami.DA_FamiliarFX_Common_Usami",BasicAttackTag=(TagName="FX.Familiar.Common.Usami.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Usami.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Usami.Hit"),DeathTag=(TagName="FX.Familiar.Common.Usami.Death"))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1168,12 +1168,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1601,11 +1595,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1989,7 +1980,7 @@
       <c r="B2">
         <v>0.7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2" t="s">
@@ -2034,10 +2025,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>291</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
         <v>19</v>
@@ -2055,33 +2046,33 @@
         <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>292</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
         <v>19</v>
@@ -2099,33 +2090,33 @@
         <v>23</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>293</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
         <v>19</v>
@@ -2137,45 +2128,45 @@
         <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K5" t="s">
         <v>23</v>
       </c>
       <c r="L5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N5" t="s">
-        <v>263</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>0.6</v>
       </c>
       <c r="C6" t="s">
-        <v>294</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F6" t="s">
         <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
         <v>21</v>
@@ -2187,33 +2178,33 @@
         <v>23</v>
       </c>
       <c r="L6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>295</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F7" t="s">
         <v>19</v>
@@ -2231,33 +2222,33 @@
         <v>23</v>
       </c>
       <c r="L7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="N7" t="s">
-        <v>264</v>
+        <v>68</v>
       </c>
       <c r="O7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="P7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B8">
         <v>0.7</v>
       </c>
       <c r="C8" t="s">
-        <v>296</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
         <v>19</v>
@@ -2275,33 +2266,33 @@
         <v>23</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M8" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="N8" t="s">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="O8" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="P8" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F9" t="s">
         <v>19</v>
@@ -2319,33 +2310,33 @@
         <v>23</v>
       </c>
       <c r="L9" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="M9" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="N9" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="O9" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="P9" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B10">
         <v>0.4</v>
       </c>
       <c r="C10" t="s">
-        <v>298</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -2363,33 +2354,33 @@
         <v>23</v>
       </c>
       <c r="L10" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="M10" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="N10" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="O10" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B11">
         <v>1.5</v>
       </c>
       <c r="C11" t="s">
-        <v>299</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F11" t="s">
         <v>19</v>
@@ -2407,33 +2398,33 @@
         <v>23</v>
       </c>
       <c r="L11" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="N11" t="s">
-        <v>266</v>
+        <v>100</v>
       </c>
       <c r="O11" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B12">
         <v>1.5</v>
       </c>
       <c r="C12" t="s">
-        <v>300</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="F12" t="s">
         <v>19</v>
@@ -2451,33 +2442,33 @@
         <v>23</v>
       </c>
       <c r="L12" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="M12" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="N12" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="O12" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="P12" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>301</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -2495,33 +2486,33 @@
         <v>23</v>
       </c>
       <c r="L13" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="M13" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="N13" t="s">
-        <v>267</v>
+        <v>116</v>
       </c>
       <c r="O13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="P13" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>302</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -2539,33 +2530,33 @@
         <v>23</v>
       </c>
       <c r="L14" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="M14" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="N14" t="s">
-        <v>268</v>
+        <v>124</v>
       </c>
       <c r="O14" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="P14" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>303</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="F15" t="s">
         <v>19</v>
@@ -2583,33 +2574,33 @@
         <v>23</v>
       </c>
       <c r="L15" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="M15" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="N15" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="O15" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="P15" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="B16">
         <v>1.5</v>
       </c>
       <c r="C16" t="s">
-        <v>304</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
         <v>19</v>
@@ -2621,39 +2612,39 @@
         <v>21</v>
       </c>
       <c r="I16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K16" t="s">
         <v>23</v>
       </c>
       <c r="L16" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="M16" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="N16" t="s">
-        <v>269</v>
+        <v>140</v>
       </c>
       <c r="O16" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="P16" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="B17">
         <v>1.3</v>
       </c>
       <c r="C17" t="s">
-        <v>305</v>
+        <v>144</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
@@ -2671,33 +2662,33 @@
         <v>23</v>
       </c>
       <c r="L17" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="M17" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N17" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="O17" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="P17" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>306</v>
+        <v>152</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="F18" t="s">
         <v>19</v>
@@ -2709,39 +2700,39 @@
         <v>21</v>
       </c>
       <c r="I18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K18" t="s">
         <v>23</v>
       </c>
       <c r="L18" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="M18" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="N18" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="O18" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="P18" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>307</v>
+        <v>160</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="F19" t="s">
         <v>19</v>
@@ -2753,39 +2744,39 @@
         <v>21</v>
       </c>
       <c r="I19" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="K19" t="s">
         <v>23</v>
       </c>
       <c r="L19" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="N19" t="s">
-        <v>270</v>
+        <v>165</v>
       </c>
       <c r="O19" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="P19" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="B20">
         <v>1.3</v>
       </c>
       <c r="C20" t="s">
-        <v>308</v>
+        <v>169</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="F20" t="s">
         <v>19</v>
@@ -2803,33 +2794,33 @@
         <v>23</v>
       </c>
       <c r="L20" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="M20" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="N20" t="s">
-        <v>271</v>
+        <v>173</v>
       </c>
       <c r="O20" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="P20" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B21">
         <v>0.8</v>
       </c>
       <c r="C21" t="s">
-        <v>309</v>
+        <v>177</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="F21" t="s">
         <v>19</v>
@@ -2847,33 +2838,33 @@
         <v>23</v>
       </c>
       <c r="L21" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="M21" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="N21" t="s">
-        <v>272</v>
+        <v>181</v>
       </c>
       <c r="O21" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="B22">
         <v>0.8</v>
       </c>
       <c r="C22" t="s">
-        <v>310</v>
+        <v>185</v>
       </c>
       <c r="D22" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="F22" t="s">
         <v>19</v>
@@ -2891,33 +2882,33 @@
         <v>23</v>
       </c>
       <c r="L22" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="M22" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="N22" t="s">
-        <v>273</v>
+        <v>189</v>
       </c>
       <c r="O22" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="P22" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>311</v>
+        <v>193</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="F23" t="s">
         <v>19</v>
@@ -2929,39 +2920,39 @@
         <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K23" t="s">
         <v>23</v>
       </c>
       <c r="L23" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="M23" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="N23" t="s">
-        <v>274</v>
+        <v>197</v>
       </c>
       <c r="O23" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="P23" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="B24">
         <v>1.2</v>
       </c>
       <c r="C24" t="s">
-        <v>312</v>
+        <v>201</v>
       </c>
       <c r="D24" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -2973,39 +2964,39 @@
         <v>21</v>
       </c>
       <c r="I24" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K24" t="s">
         <v>23</v>
       </c>
       <c r="L24" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="M24" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="N24" t="s">
-        <v>275</v>
+        <v>205</v>
       </c>
       <c r="O24" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="P24" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="B25">
         <v>1.3</v>
       </c>
       <c r="C25" t="s">
-        <v>313</v>
+        <v>209</v>
       </c>
       <c r="D25" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -3023,33 +3014,33 @@
         <v>23</v>
       </c>
       <c r="L25" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="M25" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="N25" t="s">
-        <v>276</v>
+        <v>213</v>
       </c>
       <c r="O25" t="s">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>178</v>
+        <v>216</v>
       </c>
       <c r="B26">
         <v>1.4</v>
       </c>
       <c r="C26" t="s">
-        <v>314</v>
+        <v>217</v>
       </c>
       <c r="D26" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="F26" t="s">
         <v>19</v>
@@ -3067,33 +3058,33 @@
         <v>23</v>
       </c>
       <c r="L26" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="M26" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="N26" t="s">
-        <v>277</v>
+        <v>221</v>
       </c>
       <c r="O26" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="B27">
         <v>0.3</v>
       </c>
       <c r="C27" t="s">
-        <v>315</v>
+        <v>225</v>
       </c>
       <c r="D27" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -3111,33 +3102,33 @@
         <v>23</v>
       </c>
       <c r="L27" t="s">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="M27" t="s">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="N27" t="s">
-        <v>278</v>
+        <v>229</v>
       </c>
       <c r="O27" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="P27" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="B28">
         <v>1.5</v>
       </c>
       <c r="C28" t="s">
-        <v>316</v>
+        <v>233</v>
       </c>
       <c r="D28" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
@@ -3155,33 +3146,33 @@
         <v>23</v>
       </c>
       <c r="L28" t="s">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="M28" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="N28" t="s">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="O28" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="P28" t="s">
-        <v>195</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="B29">
         <v>0.6</v>
       </c>
       <c r="C29" t="s">
-        <v>317</v>
+        <v>241</v>
       </c>
       <c r="D29" t="s">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="F29" t="s">
         <v>19</v>
@@ -3199,33 +3190,33 @@
         <v>23</v>
       </c>
       <c r="L29" t="s">
-        <v>198</v>
+        <v>243</v>
       </c>
       <c r="M29" t="s">
-        <v>199</v>
+        <v>244</v>
       </c>
       <c r="N29" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="O29" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="P29" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="B30">
         <v>1.4</v>
       </c>
       <c r="C30" t="s">
-        <v>318</v>
+        <v>249</v>
       </c>
       <c r="D30" t="s">
-        <v>203</v>
+        <v>250</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -3243,33 +3234,33 @@
         <v>23</v>
       </c>
       <c r="L30" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="N30" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="O30" t="s">
-        <v>206</v>
+        <v>254</v>
       </c>
       <c r="P30" t="s">
-        <v>207</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>208</v>
+        <v>256</v>
       </c>
       <c r="B31">
         <v>1.2</v>
       </c>
       <c r="C31" t="s">
-        <v>319</v>
+        <v>257</v>
       </c>
       <c r="D31" t="s">
-        <v>209</v>
+        <v>258</v>
       </c>
       <c r="F31" t="s">
         <v>19</v>
@@ -3287,33 +3278,33 @@
         <v>23</v>
       </c>
       <c r="L31" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="M31" t="s">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="N31" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="O31" t="s">
-        <v>212</v>
+        <v>262</v>
       </c>
       <c r="P31" t="s">
-        <v>213</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="B32">
         <v>1.5</v>
       </c>
       <c r="C32" t="s">
-        <v>320</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>215</v>
+        <v>266</v>
       </c>
       <c r="F32" t="s">
         <v>19</v>
@@ -3325,39 +3316,39 @@
         <v>21</v>
       </c>
       <c r="I32" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K32" t="s">
         <v>23</v>
       </c>
       <c r="L32" t="s">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s">
-        <v>217</v>
+        <v>268</v>
       </c>
       <c r="N32" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="O32" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="P32" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="B33">
         <v>1.2</v>
       </c>
       <c r="C33" t="s">
-        <v>321</v>
+        <v>273</v>
       </c>
       <c r="D33" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="F33" t="s">
         <v>19</v>
@@ -3375,33 +3366,33 @@
         <v>23</v>
       </c>
       <c r="L33" t="s">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s">
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="N33" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="O33" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="P33" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="B34">
         <v>0.6</v>
       </c>
       <c r="C34" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="D34" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -3419,33 +3410,33 @@
         <v>23</v>
       </c>
       <c r="L34" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="M34" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="N34" t="s">
         <v>285</v>
       </c>
       <c r="O34" t="s">
-        <v>230</v>
+        <v>286</v>
       </c>
       <c r="P34" t="s">
-        <v>231</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="B35">
         <v>0.3</v>
       </c>
       <c r="C35" t="s">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="D35" t="s">
-        <v>233</v>
+        <v>290</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -3463,33 +3454,33 @@
         <v>23</v>
       </c>
       <c r="L35" t="s">
-        <v>234</v>
+        <v>291</v>
       </c>
       <c r="M35" t="s">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="N35" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="O35" t="s">
-        <v>236</v>
+        <v>294</v>
       </c>
       <c r="P35" t="s">
-        <v>237</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>238</v>
+        <v>296</v>
       </c>
       <c r="B36">
         <v>1.5</v>
       </c>
       <c r="C36" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="D36" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
@@ -3501,39 +3492,39 @@
         <v>21</v>
       </c>
       <c r="I36" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K36" t="s">
         <v>23</v>
       </c>
       <c r="L36" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="N36" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="O36" t="s">
-        <v>242</v>
+        <v>302</v>
       </c>
       <c r="P36" t="s">
-        <v>243</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>244</v>
+        <v>304</v>
       </c>
       <c r="B37">
         <v>1.2</v>
       </c>
       <c r="C37" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="D37" t="s">
-        <v>245</v>
+        <v>306</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
@@ -3545,39 +3536,39 @@
         <v>21</v>
       </c>
       <c r="I37" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K37" t="s">
         <v>23</v>
       </c>
       <c r="L37" t="s">
-        <v>246</v>
+        <v>307</v>
       </c>
       <c r="M37" t="s">
-        <v>247</v>
+        <v>308</v>
       </c>
       <c r="N37" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="O37" t="s">
-        <v>248</v>
+        <v>310</v>
       </c>
       <c r="P37" t="s">
-        <v>249</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="B38">
         <v>0.7</v>
       </c>
       <c r="C38" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="D38" t="s">
-        <v>251</v>
+        <v>314</v>
       </c>
       <c r="F38" t="s">
         <v>19</v>
@@ -3595,33 +3586,33 @@
         <v>23</v>
       </c>
       <c r="L38" t="s">
-        <v>252</v>
+        <v>315</v>
       </c>
       <c r="M38" t="s">
-        <v>253</v>
+        <v>316</v>
       </c>
       <c r="N38" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="O38" t="s">
-        <v>254</v>
+        <v>318</v>
       </c>
       <c r="P38" t="s">
-        <v>255</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="B39">
         <v>0.7</v>
       </c>
       <c r="C39" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D39" t="s">
-        <v>257</v>
+        <v>322</v>
       </c>
       <c r="F39" t="s">
         <v>19</v>
@@ -3639,24 +3630,23 @@
         <v>23</v>
       </c>
       <c r="L39" t="s">
-        <v>258</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s">
-        <v>259</v>
+        <v>324</v>
       </c>
       <c r="N39" t="s">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="O39" t="s">
-        <v>260</v>
+        <v>326</v>
       </c>
       <c r="P39" t="s">
-        <v>261</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DesignData/Excel_Masters/FamiliarAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/FamiliarAssets_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="319">
   <si>
     <t>---</t>
   </si>
@@ -496,33 +496,6 @@
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Familiar/ForestSpirit/AM_ForestSpirit_Dead.AM_ForestSpirit_Dead</t>
-  </si>
-  <si>
-    <t>Foxhound</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/FamiliarFXAssets/Common/DA_FamiliarFX_Common_Foxhound.DA_FamiliarFX_Common_Foxhound",BasicAttackTag=(TagName="FX.Familiar.Common.Foxhound.BasicAttack"),BasicAttackHitTag=(TagName="FX.Familiar.Common.Foxhound.BasicAttackHit"),HitTag=(TagName="FX.Familiar.Common.Foxhound.Hit"),DeathTag=(TagName="FX.Familiar.Common.Foxhound.Death"))</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Attack.AM_Foxhound_Attack</t>
-  </si>
-  <si>
-    <t>(AbilityClass=None,EffectClass=None,ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Monster/Foxhound/SKM_Foxhound.SKM_Foxhound</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FoxHound.Icon_FoxHound</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Foxhound/ABP_Foxhound.ABP_Foxhound_C'</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Damage.AM_Foxhound_Damage</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Dead.AM_Foxhound_Dead</t>
   </si>
   <si>
     <t>GoldMacaron</t>
@@ -1920,7 +1893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -2726,7 +2699,7 @@
         <v>159</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="C19" t="s">
         <v>160</v>
@@ -2744,39 +2717,39 @@
         <v>21</v>
       </c>
       <c r="I19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
         <v>162</v>
       </c>
-      <c r="K19" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>163</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>164</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>165</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>166</v>
-      </c>
-      <c r="P19" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20">
+        <v>0.8</v>
+      </c>
+      <c r="C20" t="s">
         <v>168</v>
       </c>
-      <c r="B20">
-        <v>1.3</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>169</v>
-      </c>
-      <c r="D20" t="s">
-        <v>170</v>
       </c>
       <c r="F20" t="s">
         <v>19</v>
@@ -2794,33 +2767,33 @@
         <v>23</v>
       </c>
       <c r="L20" t="s">
+        <v>170</v>
+      </c>
+      <c r="M20" t="s">
         <v>171</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>172</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>173</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>174</v>
-      </c>
-      <c r="P20" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B21">
         <v>0.8</v>
       </c>
       <c r="C21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" t="s">
         <v>177</v>
-      </c>
-      <c r="D21" t="s">
-        <v>178</v>
       </c>
       <c r="F21" t="s">
         <v>19</v>
@@ -2838,33 +2811,33 @@
         <v>23</v>
       </c>
       <c r="L21" t="s">
+        <v>178</v>
+      </c>
+      <c r="M21" t="s">
         <v>179</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>180</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>181</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>182</v>
-      </c>
-      <c r="P21" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
         <v>184</v>
       </c>
-      <c r="B22">
-        <v>0.8</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>185</v>
-      </c>
-      <c r="D22" t="s">
-        <v>186</v>
       </c>
       <c r="F22" t="s">
         <v>19</v>
@@ -2876,39 +2849,39 @@
         <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="K22" t="s">
         <v>23</v>
       </c>
       <c r="L22" t="s">
+        <v>186</v>
+      </c>
+      <c r="M22" t="s">
         <v>187</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>188</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>189</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>190</v>
-      </c>
-      <c r="P22" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>191</v>
+      </c>
+      <c r="B23">
+        <v>1.2</v>
+      </c>
+      <c r="C23" t="s">
         <v>192</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>193</v>
-      </c>
-      <c r="D23" t="s">
-        <v>194</v>
       </c>
       <c r="F23" t="s">
         <v>19</v>
@@ -2926,33 +2899,33 @@
         <v>23</v>
       </c>
       <c r="L23" t="s">
+        <v>194</v>
+      </c>
+      <c r="M23" t="s">
         <v>195</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>196</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>197</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>198</v>
-      </c>
-      <c r="P23" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>199</v>
+      </c>
+      <c r="B24">
+        <v>1.3</v>
+      </c>
+      <c r="C24" t="s">
         <v>200</v>
       </c>
-      <c r="B24">
-        <v>1.2</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>201</v>
-      </c>
-      <c r="D24" t="s">
-        <v>202</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -2964,39 +2937,39 @@
         <v>21</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="K24" t="s">
         <v>23</v>
       </c>
       <c r="L24" t="s">
+        <v>202</v>
+      </c>
+      <c r="M24" t="s">
         <v>203</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>204</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>205</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>206</v>
-      </c>
-      <c r="P24" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>207</v>
+      </c>
+      <c r="B25">
+        <v>1.4</v>
+      </c>
+      <c r="C25" t="s">
         <v>208</v>
       </c>
-      <c r="B25">
-        <v>1.3</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>209</v>
-      </c>
-      <c r="D25" t="s">
-        <v>210</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -3014,33 +2987,33 @@
         <v>23</v>
       </c>
       <c r="L25" t="s">
+        <v>210</v>
+      </c>
+      <c r="M25" t="s">
         <v>211</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>212</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>213</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>214</v>
-      </c>
-      <c r="P25" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26">
+        <v>0.3</v>
+      </c>
+      <c r="C26" t="s">
         <v>216</v>
       </c>
-      <c r="B26">
-        <v>1.4</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>217</v>
-      </c>
-      <c r="D26" t="s">
-        <v>218</v>
       </c>
       <c r="F26" t="s">
         <v>19</v>
@@ -3058,33 +3031,33 @@
         <v>23</v>
       </c>
       <c r="L26" t="s">
+        <v>218</v>
+      </c>
+      <c r="M26" t="s">
         <v>219</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>220</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>221</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>222</v>
-      </c>
-      <c r="P26" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B27">
+        <v>1.5</v>
+      </c>
+      <c r="C27" t="s">
         <v>224</v>
       </c>
-      <c r="B27">
-        <v>0.3</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>225</v>
-      </c>
-      <c r="D27" t="s">
-        <v>226</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -3102,33 +3075,33 @@
         <v>23</v>
       </c>
       <c r="L27" t="s">
+        <v>226</v>
+      </c>
+      <c r="M27" t="s">
         <v>227</v>
       </c>
-      <c r="M27" t="s">
+      <c r="N27" t="s">
         <v>228</v>
       </c>
-      <c r="N27" t="s">
+      <c r="O27" t="s">
         <v>229</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>230</v>
-      </c>
-      <c r="P27" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>231</v>
+      </c>
+      <c r="B28">
+        <v>0.6</v>
+      </c>
+      <c r="C28" t="s">
         <v>232</v>
       </c>
-      <c r="B28">
-        <v>1.5</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>233</v>
-      </c>
-      <c r="D28" t="s">
-        <v>234</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
@@ -3146,33 +3119,33 @@
         <v>23</v>
       </c>
       <c r="L28" t="s">
+        <v>234</v>
+      </c>
+      <c r="M28" t="s">
         <v>235</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
         <v>236</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
         <v>237</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>238</v>
-      </c>
-      <c r="P28" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>239</v>
+      </c>
+      <c r="B29">
+        <v>1.4</v>
+      </c>
+      <c r="C29" t="s">
         <v>240</v>
       </c>
-      <c r="B29">
-        <v>0.6</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>241</v>
-      </c>
-      <c r="D29" t="s">
-        <v>242</v>
       </c>
       <c r="F29" t="s">
         <v>19</v>
@@ -3190,33 +3163,33 @@
         <v>23</v>
       </c>
       <c r="L29" t="s">
+        <v>242</v>
+      </c>
+      <c r="M29" t="s">
         <v>243</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>244</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>245</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>246</v>
-      </c>
-      <c r="P29" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>247</v>
+      </c>
+      <c r="B30">
+        <v>1.2</v>
+      </c>
+      <c r="C30" t="s">
         <v>248</v>
       </c>
-      <c r="B30">
-        <v>1.4</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>249</v>
-      </c>
-      <c r="D30" t="s">
-        <v>250</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -3234,33 +3207,33 @@
         <v>23</v>
       </c>
       <c r="L30" t="s">
+        <v>250</v>
+      </c>
+      <c r="M30" t="s">
         <v>251</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>252</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>253</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>254</v>
-      </c>
-      <c r="P30" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>255</v>
+      </c>
+      <c r="B31">
+        <v>1.5</v>
+      </c>
+      <c r="C31" t="s">
         <v>256</v>
       </c>
-      <c r="B31">
-        <v>1.2</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>257</v>
-      </c>
-      <c r="D31" t="s">
-        <v>258</v>
       </c>
       <c r="F31" t="s">
         <v>19</v>
@@ -3272,39 +3245,39 @@
         <v>21</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="K31" t="s">
         <v>23</v>
       </c>
       <c r="L31" t="s">
+        <v>258</v>
+      </c>
+      <c r="M31" t="s">
         <v>259</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>260</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>261</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>262</v>
-      </c>
-      <c r="P31" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>263</v>
+      </c>
+      <c r="B32">
+        <v>1.2</v>
+      </c>
+      <c r="C32" t="s">
         <v>264</v>
       </c>
-      <c r="B32">
-        <v>1.5</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>265</v>
-      </c>
-      <c r="D32" t="s">
-        <v>266</v>
       </c>
       <c r="F32" t="s">
         <v>19</v>
@@ -3316,39 +3289,39 @@
         <v>21</v>
       </c>
       <c r="I32" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="K32" t="s">
         <v>23</v>
       </c>
       <c r="L32" t="s">
+        <v>266</v>
+      </c>
+      <c r="M32" t="s">
         <v>267</v>
       </c>
-      <c r="M32" t="s">
+      <c r="N32" t="s">
         <v>268</v>
       </c>
-      <c r="N32" t="s">
+      <c r="O32" t="s">
         <v>269</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>270</v>
-      </c>
-      <c r="P32" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>271</v>
+      </c>
+      <c r="B33">
+        <v>0.6</v>
+      </c>
+      <c r="C33" t="s">
         <v>272</v>
       </c>
-      <c r="B33">
-        <v>1.2</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>273</v>
-      </c>
-      <c r="D33" t="s">
-        <v>274</v>
       </c>
       <c r="F33" t="s">
         <v>19</v>
@@ -3366,33 +3339,33 @@
         <v>23</v>
       </c>
       <c r="L33" t="s">
+        <v>274</v>
+      </c>
+      <c r="M33" t="s">
         <v>275</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>276</v>
       </c>
-      <c r="N33" t="s">
+      <c r="O33" t="s">
         <v>277</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>278</v>
-      </c>
-      <c r="P33" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>279</v>
+      </c>
+      <c r="B34">
+        <v>0.3</v>
+      </c>
+      <c r="C34" t="s">
         <v>280</v>
       </c>
-      <c r="B34">
-        <v>0.6</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>281</v>
-      </c>
-      <c r="D34" t="s">
-        <v>282</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -3410,33 +3383,33 @@
         <v>23</v>
       </c>
       <c r="L34" t="s">
+        <v>282</v>
+      </c>
+      <c r="M34" t="s">
         <v>283</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>284</v>
       </c>
-      <c r="N34" t="s">
+      <c r="O34" t="s">
         <v>285</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>286</v>
-      </c>
-      <c r="P34" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>287</v>
+      </c>
+      <c r="B35">
+        <v>1.5</v>
+      </c>
+      <c r="C35" t="s">
         <v>288</v>
       </c>
-      <c r="B35">
-        <v>0.3</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>289</v>
-      </c>
-      <c r="D35" t="s">
-        <v>290</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -3448,39 +3421,39 @@
         <v>21</v>
       </c>
       <c r="I35" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="K35" t="s">
         <v>23</v>
       </c>
       <c r="L35" t="s">
+        <v>290</v>
+      </c>
+      <c r="M35" t="s">
         <v>291</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" t="s">
         <v>292</v>
       </c>
-      <c r="N35" t="s">
+      <c r="O35" t="s">
         <v>293</v>
       </c>
-      <c r="O35" t="s">
+      <c r="P35" t="s">
         <v>294</v>
-      </c>
-      <c r="P35" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>295</v>
+      </c>
+      <c r="B36">
+        <v>1.2</v>
+      </c>
+      <c r="C36" t="s">
         <v>296</v>
       </c>
-      <c r="B36">
-        <v>1.5</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>297</v>
-      </c>
-      <c r="D36" t="s">
-        <v>298</v>
       </c>
       <c r="F36" t="s">
         <v>19</v>
@@ -3498,33 +3471,33 @@
         <v>23</v>
       </c>
       <c r="L36" t="s">
+        <v>298</v>
+      </c>
+      <c r="M36" t="s">
         <v>299</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" t="s">
         <v>300</v>
       </c>
-      <c r="N36" t="s">
+      <c r="O36" t="s">
         <v>301</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>302</v>
-      </c>
-      <c r="P36" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>303</v>
+      </c>
+      <c r="B37">
+        <v>0.7</v>
+      </c>
+      <c r="C37" t="s">
         <v>304</v>
       </c>
-      <c r="B37">
-        <v>1.2</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>305</v>
-      </c>
-      <c r="D37" t="s">
-        <v>306</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
@@ -3536,39 +3509,39 @@
         <v>21</v>
       </c>
       <c r="I37" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="K37" t="s">
         <v>23</v>
       </c>
       <c r="L37" t="s">
+        <v>306</v>
+      </c>
+      <c r="M37" t="s">
         <v>307</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>308</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
         <v>309</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>310</v>
-      </c>
-      <c r="P37" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B38">
         <v>0.7</v>
       </c>
       <c r="C38" t="s">
+        <v>312</v>
+      </c>
+      <c r="D38" t="s">
         <v>313</v>
-      </c>
-      <c r="D38" t="s">
-        <v>314</v>
       </c>
       <c r="F38" t="s">
         <v>19</v>
@@ -3586,63 +3559,19 @@
         <v>23</v>
       </c>
       <c r="L38" t="s">
+        <v>314</v>
+      </c>
+      <c r="M38" t="s">
         <v>315</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>316</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
         <v>317</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>318</v>
-      </c>
-      <c r="P38" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>320</v>
-      </c>
-      <c r="B39">
-        <v>0.7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>321</v>
-      </c>
-      <c r="D39" t="s">
-        <v>322</v>
-      </c>
-      <c r="F39" t="s">
-        <v>19</v>
-      </c>
-      <c r="G39" t="s">
-        <v>20</v>
-      </c>
-      <c r="H39" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" t="s">
-        <v>22</v>
-      </c>
-      <c r="K39" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" t="s">
-        <v>323</v>
-      </c>
-      <c r="M39" t="s">
-        <v>324</v>
-      </c>
-      <c r="N39" t="s">
-        <v>325</v>
-      </c>
-      <c r="O39" t="s">
-        <v>326</v>
-      </c>
-      <c r="P39" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>
